--- a/data_source/shp/data_EEZ_areas_by_zone.xlsx
+++ b/data_source/shp/data_EEZ_areas_by_zone.xlsx
@@ -1,16 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aurel\Desktop\M2\Stage ecoseas-csm\CSM\bcw-paper-2025\data_source\shp\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE70D9C-DEF2-451C-96EB-FC9CEDAF2997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="13110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="dissolved_EEZ" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="dissolved_EEZ" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="617">
   <si>
     <t>UNION</t>
   </si>
@@ -1866,29 +1876,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt formatCode="GENERAL" numFmtId="164"/>
-    <numFmt formatCode="DD/MM/YY" numFmtId="165"/>
-    <numFmt formatCode="DD/MM/YYYY\ HH:MM:SS" numFmtId="166"/>
-    <numFmt formatCode="HH:MM:SS" numFmtId="167"/>
-    <numFmt formatCode="DD/MM/YYYY\ HH:MM:SS.000" numFmtId="168"/>
-    <numFmt formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;" numFmtId="169"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="1">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
   </fills>
   <borders count="1">
-    <border diagonalDown="false" diagonalUp="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1897,60 +1902,351 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="164">
-</xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" xfId="0"/>
-    <xf numFmtId="165" xfId="0"/>
-    <xf numFmtId="166" xfId="0"/>
-    <xf numFmtId="167" xfId="0"/>
-    <xf numFmtId="168" xfId="0"/>
-    <xf numFmtId="169" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" customBuiltin="false" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE329"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1024" width="15"/>
-    <col min="2" max="1024" width="15"/>
-    <col min="3" max="1024" width="15"/>
-    <col min="4" max="1024" width="15"/>
-    <col min="5" max="1024" width="15"/>
-    <col min="6" max="1024" width="15"/>
-    <col min="7" max="1024" width="15"/>
-    <col min="8" max="1024" width="15"/>
-    <col min="9" max="1024" width="15"/>
-    <col min="10" max="1024" width="15"/>
-    <col min="11" max="1024" width="15"/>
-    <col min="12" max="1024" width="15"/>
-    <col min="13" max="1024" width="15"/>
-    <col min="14" max="1024" width="15"/>
-    <col min="15" max="1024" width="15"/>
-    <col min="16" max="1024" width="15"/>
-    <col min="17" max="1024" width="15"/>
-    <col min="18" max="1024" width="15"/>
-    <col min="19" max="1024" width="15"/>
-    <col min="20" max="1024" width="15"/>
-    <col min="21" max="1024" width="15"/>
-    <col min="22" max="1024" width="15"/>
-    <col min="23" max="1024" width="15"/>
-    <col min="24" max="1024" width="15"/>
-    <col min="25" max="1024" width="15"/>
-    <col min="26" max="1024" width="15"/>
-    <col min="27" max="1024" width="15"/>
-    <col min="28" max="1024" width="15"/>
-    <col min="29" max="1024" width="15"/>
-    <col min="30" max="1024" width="15"/>
-    <col min="31" max="1024" width="15"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2045,7 +2341,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -2083,16 +2379,16 @@
         <v>25.0992</v>
       </c>
       <c r="AC2">
-        <v>-75.59989</v>
+        <v>-75.599890000000002</v>
       </c>
       <c r="AD2">
         <v>633060</v>
       </c>
       <c r="AE2">
-        <v>633060.0463</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>633060.04630000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -2145,7 +2441,7 @@
         <v>26.01295</v>
       </c>
       <c r="AC3">
-        <v>55.17177</v>
+        <v>55.171770000000002</v>
       </c>
       <c r="AD3">
         <v>6199</v>
@@ -2154,7 +2450,7 @@
         <v>6199.306012</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -2189,19 +2485,19 @@
         <v>33</v>
       </c>
       <c r="AB4">
-        <v>-42.70891</v>
+        <v>-42.708910000000003</v>
       </c>
       <c r="AC4">
-        <v>77.74891</v>
+        <v>77.748909999999995</v>
       </c>
       <c r="AD4">
         <v>4374136</v>
       </c>
       <c r="AE4">
-        <v>4374135.887</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>4374135.8870000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -2236,10 +2532,10 @@
         <v>33</v>
       </c>
       <c r="AB5">
-        <v>8.532069999999999</v>
+        <v>8.5320699999999992</v>
       </c>
       <c r="AC5">
-        <v>2.35613</v>
+        <v>2.3561299999999998</v>
       </c>
       <c r="AD5">
         <v>150707</v>
@@ -2248,7 +2544,7 @@
         <v>150707.2389</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -2289,10 +2585,10 @@
         <v>338839</v>
       </c>
       <c r="AE6">
-        <v>338839.1232</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>338839.12319999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -2339,7 +2635,7 @@
         <v>1742905.72</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -2398,7 +2694,7 @@
         <v>56</v>
       </c>
       <c r="AB8">
-        <v>60.03609</v>
+        <v>60.036090000000002</v>
       </c>
       <c r="AC8">
         <v>-7.51858</v>
@@ -2407,10 +2703,10 @@
         <v>8011</v>
       </c>
       <c r="AE8">
-        <v>8010.585775</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>8010.5857749999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -2442,7 +2738,7 @@
         <v>59</v>
       </c>
       <c r="AB9">
-        <v>47.58715</v>
+        <v>47.587150000000001</v>
       </c>
       <c r="AC9">
         <v>14.14156</v>
@@ -2451,10 +2747,10 @@
         <v>83989</v>
       </c>
       <c r="AE9">
-        <v>83989.03008</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>83989.030079999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -2498,10 +2794,10 @@
         <v>4438697</v>
       </c>
       <c r="AE10">
-        <v>4438697.451</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>4438697.4510000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2563,16 +2859,16 @@
         <v>-13.21377</v>
       </c>
       <c r="AC11">
-        <v>45.30528</v>
+        <v>45.305280000000003</v>
       </c>
       <c r="AD11">
         <v>67285</v>
       </c>
       <c r="AE11">
-        <v>67285.12793</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>67285.127930000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -2607,7 +2903,7 @@
         <v>33</v>
       </c>
       <c r="AB12">
-        <v>52.72797</v>
+        <v>52.727969999999999</v>
       </c>
       <c r="AC12">
         <v>-11.24282</v>
@@ -2616,10 +2912,10 @@
         <v>498255</v>
       </c>
       <c r="AE12">
-        <v>498255.4494</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>498255.44939999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -2654,19 +2950,19 @@
         <v>33</v>
       </c>
       <c r="AB13">
-        <v>65.75821999999999</v>
+        <v>65.758219999999994</v>
       </c>
       <c r="AC13">
-        <v>95.43783000000001</v>
+        <v>95.437830000000005</v>
       </c>
       <c r="AD13">
         <v>24610609</v>
       </c>
       <c r="AE13">
-        <v>24610608.92</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>24610608.920000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -2704,16 +3000,16 @@
         <v>13.32253</v>
       </c>
       <c r="AC14">
-        <v>-57.99722</v>
+        <v>-57.997219999999999</v>
       </c>
       <c r="AD14">
         <v>185441</v>
       </c>
       <c r="AE14">
-        <v>185441.1234</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>185441.12340000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -2781,10 +3077,10 @@
         <v>8478</v>
       </c>
       <c r="AE15">
-        <v>8478.168309999999</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>8478.1683099999991</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>77</v>
       </c>
@@ -2828,10 +3124,10 @@
         <v>764117</v>
       </c>
       <c r="AE16">
-        <v>764117.3578999999</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>764117.35789999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -2890,10 +3186,10 @@
         <v>56</v>
       </c>
       <c r="AB17">
-        <v>2.0676</v>
+        <v>2.0676000000000001</v>
       </c>
       <c r="AC17">
-        <v>5.58699</v>
+        <v>5.5869900000000001</v>
       </c>
       <c r="AD17">
         <v>34534</v>
@@ -2902,7 +3198,7 @@
         <v>34533.74955</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -2937,10 +3233,10 @@
         <v>33</v>
       </c>
       <c r="AB18">
-        <v>42.24675</v>
+        <v>42.246749999999999</v>
       </c>
       <c r="AC18">
-        <v>42.77446</v>
+        <v>42.774459999999998</v>
       </c>
       <c r="AD18">
         <v>92515</v>
@@ -2949,7 +3245,7 @@
         <v>92515.43535</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -2984,19 +3280,19 @@
         <v>33</v>
       </c>
       <c r="AB19">
-        <v>8.329140000000002</v>
+        <v>8.3291400000000024</v>
       </c>
       <c r="AC19">
-        <v>-80.30123</v>
+        <v>-80.301230000000004</v>
       </c>
       <c r="AD19">
         <v>406250</v>
       </c>
       <c r="AE19">
-        <v>406250.2226</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>406250.22259999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>88</v>
       </c>
@@ -3031,7 +3327,7 @@
         <v>33</v>
       </c>
       <c r="AB20">
-        <v>51.61305</v>
+        <v>51.613050000000001</v>
       </c>
       <c r="AC20">
         <v>10.09878</v>
@@ -3040,10 +3336,10 @@
         <v>414273</v>
       </c>
       <c r="AE20">
-        <v>414273.458</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>414273.45799999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -3087,10 +3383,10 @@
         <v>1342014</v>
       </c>
       <c r="AE21">
-        <v>1342014.332</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>1342014.3319999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -3125,10 +3421,10 @@
         <v>33</v>
       </c>
       <c r="AB22">
-        <v>18.56077</v>
+        <v>18.560770000000002</v>
       </c>
       <c r="AC22">
-        <v>95.73341000000001</v>
+        <v>95.733410000000006</v>
       </c>
       <c r="AD22">
         <v>1165257</v>
@@ -3137,7 +3433,7 @@
         <v>1165256.57</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -3166,19 +3462,19 @@
         <v>33</v>
       </c>
       <c r="AB23">
-        <v>-20.50277</v>
+        <v>-20.502770000000002</v>
       </c>
       <c r="AC23">
-        <v>-29.09644</v>
+        <v>-29.096440000000001</v>
       </c>
       <c r="AD23">
         <v>472493</v>
       </c>
       <c r="AE23">
-        <v>472492.5991</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>472492.59909999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -3213,19 +3509,19 @@
         <v>33</v>
       </c>
       <c r="AB24">
-        <v>19.15407</v>
+        <v>19.154070000000001</v>
       </c>
       <c r="AC24">
-        <v>-81.13855</v>
+        <v>-81.138549999999995</v>
       </c>
       <c r="AD24">
         <v>118567</v>
       </c>
       <c r="AE24">
-        <v>118567.3013</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>118567.30130000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>100</v>
       </c>
@@ -3260,19 +3556,19 @@
         <v>33</v>
       </c>
       <c r="AB25">
-        <v>6.44434</v>
+        <v>6.4443400000000004</v>
       </c>
       <c r="AC25">
-        <v>133.07051</v>
+        <v>133.07051000000001</v>
       </c>
       <c r="AD25">
         <v>616993</v>
       </c>
       <c r="AE25">
-        <v>616992.7204</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>616992.72039999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -3307,19 +3603,19 @@
         <v>33</v>
       </c>
       <c r="AB26">
-        <v>-13.85503</v>
+        <v>-13.855029999999999</v>
       </c>
       <c r="AC26">
-        <v>-169.06414</v>
+        <v>-169.06414000000001</v>
       </c>
       <c r="AD26">
         <v>406038</v>
       </c>
       <c r="AE26">
-        <v>406038.4238</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>406038.42379999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -3393,10 +3689,10 @@
         <v>73801</v>
       </c>
       <c r="AE27">
-        <v>73800.91173000001</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>73800.911730000007</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>107</v>
       </c>
@@ -3434,16 +3730,16 @@
         <v>5.79819</v>
       </c>
       <c r="AC28">
-        <v>-1.03492</v>
+        <v>-1.0349200000000001</v>
       </c>
       <c r="AD28">
         <v>466118</v>
       </c>
       <c r="AE28">
-        <v>466117.5817</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>466117.58169999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -3478,19 +3774,19 @@
         <v>33</v>
       </c>
       <c r="AB29">
-        <v>32.2405</v>
+        <v>32.240499999999997</v>
       </c>
       <c r="AC29">
-        <v>54.25495</v>
+        <v>54.254950000000001</v>
       </c>
       <c r="AD29">
         <v>1838516</v>
       </c>
       <c r="AE29">
-        <v>1838516.136</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>1838516.1359999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>109</v>
       </c>
@@ -3522,19 +3818,19 @@
         <v>59</v>
       </c>
       <c r="AB30">
-        <v>-19.00011</v>
+        <v>-19.000109999999999</v>
       </c>
       <c r="AC30">
-        <v>29.87213</v>
+        <v>29.872129999999999</v>
       </c>
       <c r="AD30">
         <v>390690</v>
       </c>
       <c r="AE30">
-        <v>390689.6313</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>390689.63130000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>111</v>
       </c>
@@ -3596,7 +3892,7 @@
         <v>-3.38855</v>
       </c>
       <c r="AC31">
-        <v>-82.53292999999999</v>
+        <v>-82.532929999999993</v>
       </c>
       <c r="AD31">
         <v>16091</v>
@@ -3605,7 +3901,7 @@
         <v>16091.21164</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>116</v>
       </c>
@@ -3649,10 +3945,10 @@
         <v>346871</v>
       </c>
       <c r="AE32">
-        <v>346871.3948</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>346871.39480000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>118</v>
       </c>
@@ -3687,10 +3983,10 @@
         <v>33</v>
       </c>
       <c r="AB33">
-        <v>19.98315</v>
+        <v>19.983149999999998</v>
       </c>
       <c r="AC33">
-        <v>-11.40201</v>
+        <v>-11.402010000000001</v>
       </c>
       <c r="AD33">
         <v>1212055</v>
@@ -3699,7 +3995,7 @@
         <v>1212054.797</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>120</v>
       </c>
@@ -3734,19 +4030,19 @@
         <v>33</v>
       </c>
       <c r="AB34">
-        <v>9.08403</v>
+        <v>9.0840300000000003</v>
       </c>
       <c r="AC34">
-        <v>-66.06931</v>
+        <v>-66.069310000000002</v>
       </c>
       <c r="AD34">
         <v>1383023</v>
       </c>
       <c r="AE34">
-        <v>1383023.211</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>1383023.2109999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>122</v>
       </c>
@@ -3808,16 +4104,16 @@
         <v>41.30715</v>
       </c>
       <c r="AC35">
-        <v>9.048859999999999</v>
+        <v>9.0488599999999995</v>
       </c>
       <c r="AD35">
         <v>67</v>
       </c>
       <c r="AE35">
-        <v>67.04130144</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>67.041301439999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>125</v>
       </c>
@@ -3852,10 +4148,10 @@
         <v>33</v>
       </c>
       <c r="AB36">
-        <v>18.12544</v>
+        <v>18.125440000000001</v>
       </c>
       <c r="AC36">
-        <v>-73.36919</v>
+        <v>-73.369190000000003</v>
       </c>
       <c r="AD36">
         <v>130503</v>
@@ -3864,7 +4160,7 @@
         <v>130502.8419</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>127</v>
       </c>
@@ -3899,7 +4195,7 @@
         <v>33</v>
       </c>
       <c r="AB37">
-        <v>13.87849</v>
+        <v>13.878489999999999</v>
       </c>
       <c r="AC37">
         <v>-61.09834</v>
@@ -3911,7 +4207,7 @@
         <v>16027.46852</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>129</v>
       </c>
@@ -3973,16 +4269,16 @@
         <v>31.85716</v>
       </c>
       <c r="AC38">
-        <v>35.05672</v>
+        <v>35.056719999999999</v>
       </c>
       <c r="AD38">
         <v>7373</v>
       </c>
       <c r="AE38">
-        <v>7372.715335</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>7372.7153349999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>133</v>
       </c>
@@ -4017,19 +4313,19 @@
         <v>33</v>
       </c>
       <c r="AB39">
-        <v>35.87951</v>
+        <v>35.879510000000003</v>
       </c>
       <c r="AC39">
-        <v>127.62547</v>
+        <v>127.62547000000001</v>
       </c>
       <c r="AD39">
         <v>448099</v>
       </c>
       <c r="AE39">
-        <v>448099.2543</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>448099.25429999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>135</v>
       </c>
@@ -4076,10 +4372,10 @@
         <v>39</v>
       </c>
       <c r="AB40">
-        <v>22.49336</v>
+        <v>22.493359999999999</v>
       </c>
       <c r="AC40">
-        <v>36.22526</v>
+        <v>36.225259999999999</v>
       </c>
       <c r="AD40">
         <v>37611</v>
@@ -4088,7 +4384,7 @@
         <v>37610.64963</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>141</v>
       </c>
@@ -4123,10 +4419,10 @@
         <v>33</v>
       </c>
       <c r="AB41">
-        <v>-17.94724</v>
+        <v>-17.947240000000001</v>
       </c>
       <c r="AC41">
-        <v>94.27352</v>
+        <v>94.273520000000005</v>
       </c>
       <c r="AD41">
         <v>1315158</v>
@@ -4135,7 +4431,7 @@
         <v>1315157.77</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -4164,19 +4460,19 @@
         <v>33</v>
       </c>
       <c r="AB42">
-        <v>-46.83294</v>
+        <v>-46.832940000000001</v>
       </c>
       <c r="AC42">
-        <v>37.80851</v>
+        <v>37.808509999999998</v>
       </c>
       <c r="AD42">
         <v>475240</v>
       </c>
       <c r="AE42">
-        <v>475239.5011</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>475239.50109999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>146</v>
       </c>
@@ -4211,19 +4507,19 @@
         <v>33</v>
       </c>
       <c r="AB43">
-        <v>45.6669</v>
+        <v>45.666899999999998</v>
       </c>
       <c r="AC43">
-        <v>25.5328</v>
+        <v>25.532800000000002</v>
       </c>
       <c r="AD43">
         <v>267908</v>
       </c>
       <c r="AE43">
-        <v>267907.8796</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>267907.87959999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>148</v>
       </c>
@@ -4261,7 +4557,7 @@
         <v>-0.25894</v>
       </c>
       <c r="AC44">
-        <v>172.78257</v>
+        <v>172.78256999999999</v>
       </c>
       <c r="AD44">
         <v>1053609</v>
@@ -4270,7 +4566,7 @@
         <v>1053608.601</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>151</v>
       </c>
@@ -4305,19 +4601,19 @@
         <v>33</v>
       </c>
       <c r="AB45">
-        <v>33.03873</v>
+        <v>33.038730000000001</v>
       </c>
       <c r="AC45">
-        <v>43.78005</v>
+        <v>43.780050000000003</v>
       </c>
       <c r="AD45">
         <v>438532</v>
       </c>
       <c r="AE45">
-        <v>438531.6527</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>438531.65269999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>153</v>
       </c>
@@ -4349,19 +4645,19 @@
         <v>59</v>
       </c>
       <c r="AB46">
-        <v>17.36075</v>
+        <v>17.360749999999999</v>
       </c>
       <c r="AC46">
-        <v>-3.52242</v>
+        <v>-3.5224199999999999</v>
       </c>
       <c r="AD46">
         <v>1252545</v>
       </c>
       <c r="AE46">
-        <v>1252545.079</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>1252545.0789999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>155</v>
       </c>
@@ -4405,10 +4701,10 @@
         <v>434897</v>
       </c>
       <c r="AE47">
-        <v>434897.4775</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>434897.47749999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>158</v>
       </c>
@@ -4443,7 +4739,7 @@
         <v>33</v>
       </c>
       <c r="AB48">
-        <v>-8.63292</v>
+        <v>-8.6329200000000004</v>
       </c>
       <c r="AC48">
         <v>-172.08471</v>
@@ -4452,10 +4748,10 @@
         <v>320756</v>
       </c>
       <c r="AE48">
-        <v>320755.744</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>320755.74400000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>160</v>
       </c>
@@ -4490,19 +4786,19 @@
         <v>33</v>
       </c>
       <c r="AB49">
-        <v>13.36799</v>
+        <v>13.367990000000001</v>
       </c>
       <c r="AC49">
-        <v>-17.4335</v>
+        <v>-17.433499999999999</v>
       </c>
       <c r="AD49">
         <v>33723</v>
       </c>
       <c r="AE49">
-        <v>33723.36947</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>33723.369469999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>162</v>
       </c>
@@ -4537,7 +4833,7 @@
         <v>33</v>
       </c>
       <c r="AB50">
-        <v>61.98891</v>
+        <v>61.988909999999997</v>
       </c>
       <c r="AC50">
         <v>17.07957</v>
@@ -4546,10 +4842,10 @@
         <v>605472</v>
       </c>
       <c r="AE50">
-        <v>605471.911</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>605471.91099999996</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>164</v>
       </c>
@@ -4596,7 +4892,7 @@
         <v>446104.7597</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>166</v>
       </c>
@@ -4631,19 +4927,19 @@
         <v>33</v>
       </c>
       <c r="AB52">
-        <v>-26.33091</v>
+        <v>-26.330909999999999</v>
       </c>
       <c r="AC52">
-        <v>-79.99086</v>
+        <v>-79.990859999999998</v>
       </c>
       <c r="AD52">
         <v>450968</v>
       </c>
       <c r="AE52">
-        <v>450968.2044</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>450968.20439999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>169</v>
       </c>
@@ -4690,7 +4986,7 @@
         <v>1969814.156</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>171</v>
       </c>
@@ -4725,19 +5021,19 @@
         <v>33</v>
       </c>
       <c r="AB54">
-        <v>5.62533</v>
+        <v>5.6253299999999999</v>
       </c>
       <c r="AC54">
-        <v>12.63665</v>
+        <v>12.636649999999999</v>
       </c>
       <c r="AD54">
         <v>480130</v>
       </c>
       <c r="AE54">
-        <v>480130.3404</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>480130.34039999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>173</v>
       </c>
@@ -4769,19 +5065,19 @@
         <v>59</v>
       </c>
       <c r="AB55">
-        <v>7.27955</v>
+        <v>7.2795500000000004</v>
       </c>
       <c r="AC55">
-        <v>30.34933</v>
+        <v>30.349329999999998</v>
       </c>
       <c r="AD55">
         <v>632552</v>
       </c>
       <c r="AE55">
-        <v>632552.3626</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>632552.36259999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>175</v>
       </c>
@@ -4816,10 +5112,10 @@
         <v>33</v>
       </c>
       <c r="AB56">
-        <v>23.94815</v>
+        <v>23.948149999999998</v>
       </c>
       <c r="AC56">
-        <v>44.13136</v>
+        <v>44.131360000000001</v>
       </c>
       <c r="AD56">
         <v>2149313</v>
@@ -4828,7 +5124,7 @@
         <v>2149313.361</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>177</v>
       </c>
@@ -4863,19 +5159,19 @@
         <v>33</v>
       </c>
       <c r="AB57">
-        <v>-6.45858</v>
+        <v>-6.4585800000000004</v>
       </c>
       <c r="AC57">
-        <v>36.11885</v>
+        <v>36.118850000000002</v>
       </c>
       <c r="AD57">
         <v>1182383</v>
       </c>
       <c r="AE57">
-        <v>1182382.508</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>1182382.5079999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>179</v>
       </c>
@@ -4910,19 +5206,19 @@
         <v>33</v>
       </c>
       <c r="AB58">
-        <v>1.31326</v>
+        <v>1.3132600000000001</v>
       </c>
       <c r="AC58">
-        <v>103.82193</v>
+        <v>103.82192999999999</v>
       </c>
       <c r="AD58">
         <v>1377</v>
       </c>
       <c r="AE58">
-        <v>1377.156656</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>1377.1566560000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>181</v>
       </c>
@@ -4957,10 +5253,10 @@
         <v>33</v>
       </c>
       <c r="AB59">
-        <v>6.7689</v>
+        <v>6.7689000000000004</v>
       </c>
       <c r="AC59">
-        <v>150.32344</v>
+        <v>150.32344000000001</v>
       </c>
       <c r="AD59">
         <v>3009868</v>
@@ -4969,7 +5265,7 @@
         <v>3009867.645</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>183</v>
       </c>
@@ -5007,16 +5303,16 @@
         <v>12.8284</v>
       </c>
       <c r="AC60">
-        <v>-84.07465000000001</v>
+        <v>-84.074650000000005</v>
       </c>
       <c r="AD60">
         <v>341809</v>
       </c>
       <c r="AE60">
-        <v>341809.2869</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>341809.28690000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>185</v>
       </c>
@@ -5063,19 +5359,19 @@
         <v>39</v>
       </c>
       <c r="AB61">
-        <v>35.30805</v>
+        <v>35.308050000000001</v>
       </c>
       <c r="AC61">
-        <v>-2.92826</v>
+        <v>-2.9282599999999999</v>
       </c>
       <c r="AD61">
         <v>41</v>
       </c>
       <c r="AE61">
-        <v>40.73956715</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>40.739567149999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>190</v>
       </c>
@@ -5107,19 +5403,19 @@
         <v>59</v>
       </c>
       <c r="AB62">
-        <v>47.14144</v>
+        <v>47.141440000000003</v>
       </c>
       <c r="AC62">
-        <v>9.552580000000001</v>
+        <v>9.5525800000000007</v>
       </c>
       <c r="AD62">
         <v>161</v>
       </c>
       <c r="AE62">
-        <v>160.8089954</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>160.80899539999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>192</v>
       </c>
@@ -5154,19 +5450,19 @@
         <v>33</v>
       </c>
       <c r="AB63">
-        <v>48.02287</v>
+        <v>48.022869999999998</v>
       </c>
       <c r="AC63">
-        <v>66.68429999999999</v>
+        <v>66.684299999999993</v>
       </c>
       <c r="AD63">
         <v>2836836</v>
       </c>
       <c r="AE63">
-        <v>2836835.689</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>2836835.6889999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>194</v>
       </c>
@@ -5204,16 +5500,16 @@
         <v>22.79862</v>
       </c>
       <c r="AC64">
-        <v>-70.864</v>
+        <v>-70.864000000000004</v>
       </c>
       <c r="AD64">
         <v>92017</v>
       </c>
       <c r="AE64">
-        <v>92016.57957</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>92016.579570000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>196</v>
       </c>
@@ -5248,19 +5544,19 @@
         <v>33</v>
       </c>
       <c r="AB65">
-        <v>-39.07001</v>
+        <v>-39.070010000000003</v>
       </c>
       <c r="AC65">
-        <v>-64.22086</v>
+        <v>-64.220860000000002</v>
       </c>
       <c r="AD65">
         <v>3850468</v>
       </c>
       <c r="AE65">
-        <v>3850468.218</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>3850468.2179999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>198</v>
       </c>
@@ -5304,10 +5600,10 @@
         <v>5138717</v>
       </c>
       <c r="AE66">
-        <v>5138716.724</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>5138716.7240000004</v>
+      </c>
+    </row>
+    <row r="67" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>200</v>
       </c>
@@ -5342,7 +5638,7 @@
         <v>15.37538</v>
       </c>
       <c r="AC67">
-        <v>18.66806</v>
+        <v>18.668060000000001</v>
       </c>
       <c r="AD67">
         <v>1270767</v>
@@ -5351,7 +5647,7 @@
         <v>1270766.578</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>202</v>
       </c>
@@ -5398,7 +5694,7 @@
         <v>230091.0526</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>204</v>
       </c>
@@ -5433,19 +5729,19 @@
         <v>33</v>
       </c>
       <c r="AB69">
-        <v>33.94151</v>
+        <v>33.941510000000001</v>
       </c>
       <c r="AC69">
-        <v>35.27546</v>
+        <v>35.275460000000002</v>
       </c>
       <c r="AD69">
         <v>29064</v>
       </c>
       <c r="AE69">
-        <v>29064.42192</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>29064.421920000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>206</v>
       </c>
@@ -5480,10 +5776,10 @@
         <v>33</v>
       </c>
       <c r="AB70">
-        <v>-10.02457</v>
+        <v>-10.024570000000001</v>
       </c>
       <c r="AC70">
-        <v>163.61386</v>
+        <v>163.61385999999999</v>
       </c>
       <c r="AD70">
         <v>1631261</v>
@@ -5492,7 +5788,7 @@
         <v>1631260.53</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>208</v>
       </c>
@@ -5524,19 +5820,19 @@
         <v>59</v>
       </c>
       <c r="AB71">
-        <v>28.2595</v>
+        <v>28.259499999999999</v>
       </c>
       <c r="AC71">
-        <v>83.94394</v>
+        <v>83.943939999999998</v>
       </c>
       <c r="AD71">
         <v>147297</v>
       </c>
       <c r="AE71">
-        <v>147296.9028</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>147296.90280000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>210</v>
       </c>
@@ -5568,19 +5864,19 @@
         <v>59</v>
       </c>
       <c r="AB72">
-        <v>-3.366</v>
+        <v>-3.3660000000000001</v>
       </c>
       <c r="AC72">
-        <v>29.89129</v>
+        <v>29.891290000000001</v>
       </c>
       <c r="AD72">
         <v>26833</v>
       </c>
       <c r="AE72">
-        <v>26832.74372</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>26832.743719999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>212</v>
       </c>
@@ -5615,10 +5911,10 @@
         <v>33</v>
       </c>
       <c r="AB73">
-        <v>56.9308</v>
+        <v>56.930799999999998</v>
       </c>
       <c r="AC73">
-        <v>23.83336</v>
+        <v>23.833359999999999</v>
       </c>
       <c r="AD73">
         <v>92873</v>
@@ -5627,7 +5923,7 @@
         <v>92872.99497</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>214</v>
       </c>
@@ -5659,19 +5955,19 @@
         <v>59</v>
       </c>
       <c r="AB74">
-        <v>53.54203</v>
+        <v>53.542029999999997</v>
       </c>
       <c r="AC74">
-        <v>28.04934</v>
+        <v>28.049340000000001</v>
       </c>
       <c r="AD74">
         <v>207595</v>
       </c>
       <c r="AE74">
-        <v>207594.6878</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>207594.68780000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -5706,19 +6002,19 @@
         <v>33</v>
       </c>
       <c r="AB75">
-        <v>8.700419999999999</v>
+        <v>8.7004199999999994</v>
       </c>
       <c r="AC75">
-        <v>7.56884</v>
+        <v>7.5688399999999998</v>
       </c>
       <c r="AD75">
         <v>1087016</v>
       </c>
       <c r="AE75">
-        <v>1087016.427</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>1087016.4269999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>216</v>
       </c>
@@ -5750,19 +6046,19 @@
         <v>59</v>
       </c>
       <c r="AB76">
-        <v>6.57694</v>
+        <v>6.5769399999999996</v>
       </c>
       <c r="AC76">
-        <v>20.48641</v>
+        <v>20.486409999999999</v>
       </c>
       <c r="AD76">
         <v>620253</v>
       </c>
       <c r="AE76">
-        <v>620252.6857</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>620252.68570000003</v>
+      </c>
+    </row>
+    <row r="77" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>218</v>
       </c>
@@ -5797,19 +6093,19 @@
         <v>33</v>
       </c>
       <c r="AB77">
-        <v>-53.49828</v>
+        <v>-53.498280000000001</v>
       </c>
       <c r="AC77">
-        <v>73.73032000000001</v>
+        <v>73.730320000000006</v>
       </c>
       <c r="AD77">
         <v>417685</v>
       </c>
       <c r="AE77">
-        <v>417684.5825</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>417684.58250000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>222</v>
       </c>
@@ -5841,19 +6137,19 @@
         <v>59</v>
       </c>
       <c r="AB78">
-        <v>41.7608</v>
+        <v>41.760800000000003</v>
       </c>
       <c r="AC78">
-        <v>63.14047</v>
+        <v>63.140470000000001</v>
       </c>
       <c r="AD78">
         <v>447321</v>
       </c>
       <c r="AE78">
-        <v>447320.9324</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>447320.93239999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>224</v>
       </c>
@@ -5912,19 +6208,19 @@
         <v>39</v>
       </c>
       <c r="AB79">
-        <v>29.87235</v>
+        <v>29.872350000000001</v>
       </c>
       <c r="AC79">
-        <v>48.69255</v>
+        <v>48.692549999999997</v>
       </c>
       <c r="AD79">
         <v>28</v>
       </c>
       <c r="AE79">
-        <v>27.70172116</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>27.701721160000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>225</v>
       </c>
@@ -5983,7 +6279,7 @@
         <v>56</v>
       </c>
       <c r="AB80">
-        <v>63.15298</v>
+        <v>63.152979999999999</v>
       </c>
       <c r="AC80">
         <v>-10.98204</v>
@@ -5995,7 +6291,7 @@
         <v>1233.688465</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>228</v>
       </c>
@@ -6030,19 +6326,19 @@
         <v>33</v>
       </c>
       <c r="AB81">
-        <v>16.09117</v>
+        <v>16.091170000000002</v>
       </c>
       <c r="AC81">
-        <v>-24.17066</v>
+        <v>-24.170660000000002</v>
       </c>
       <c r="AD81">
         <v>806027</v>
       </c>
       <c r="AE81">
-        <v>806027.0355999999</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>806027.03559999994</v>
+      </c>
+    </row>
+    <row r="82" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -6080,16 +6376,16 @@
         <v>-10.26493</v>
       </c>
       <c r="AC82">
-        <v>-76.16929</v>
+        <v>-76.169290000000004</v>
       </c>
       <c r="AD82">
         <v>2146766</v>
       </c>
       <c r="AE82">
-        <v>2146765.779</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>2146765.7790000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>230</v>
       </c>
@@ -6121,7 +6417,7 @@
         <v>59</v>
       </c>
       <c r="AB83">
-        <v>18.49836</v>
+        <v>18.498360000000002</v>
       </c>
       <c r="AC83">
         <v>103.76958</v>
@@ -6130,10 +6426,10 @@
         <v>229725</v>
       </c>
       <c r="AE83">
-        <v>229724.7134</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>229724.71340000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>232</v>
       </c>
@@ -6192,7 +6488,7 @@
         <v>56</v>
       </c>
       <c r="AB84">
-        <v>30.81396</v>
+        <v>30.813960000000002</v>
       </c>
       <c r="AC84">
         <v>127.57808</v>
@@ -6201,10 +6497,10 @@
         <v>82610</v>
       </c>
       <c r="AE84">
-        <v>82609.98162000001</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>82609.981620000006</v>
+      </c>
+    </row>
+    <row r="85" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>233</v>
       </c>
@@ -6239,19 +6535,19 @@
         <v>33</v>
       </c>
       <c r="AB85">
-        <v>6.66455</v>
+        <v>6.6645500000000002</v>
       </c>
       <c r="AC85">
-        <v>81.53292999999999</v>
+        <v>81.532929999999993</v>
       </c>
       <c r="AD85">
         <v>599363</v>
       </c>
       <c r="AE85">
-        <v>599363.0095</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>599363.00950000004</v>
+      </c>
+    </row>
+    <row r="86" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>235</v>
       </c>
@@ -6301,7 +6597,7 @@
         <v>-23.2791</v>
       </c>
       <c r="AC86">
-        <v>172.03655</v>
+        <v>172.03655000000001</v>
       </c>
       <c r="AD86">
         <v>187186</v>
@@ -6310,7 +6606,7 @@
         <v>187185.5177</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>238</v>
       </c>
@@ -6348,16 +6644,16 @@
         <v>-15.97278</v>
       </c>
       <c r="AC87">
-        <v>-5.70869</v>
+        <v>-5.7086899999999998</v>
       </c>
       <c r="AD87">
         <v>449352</v>
       </c>
       <c r="AE87">
-        <v>449352.0558</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>449352.05579999997</v>
+      </c>
+    </row>
+    <row r="88" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>239</v>
       </c>
@@ -6416,10 +6712,10 @@
         <v>56</v>
       </c>
       <c r="AB88">
-        <v>11.261</v>
+        <v>11.260999999999999</v>
       </c>
       <c r="AC88">
-        <v>-18.77443</v>
+        <v>-18.774429999999999</v>
       </c>
       <c r="AD88">
         <v>63460</v>
@@ -6428,7 +6724,7 @@
         <v>63460.20895</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>244</v>
       </c>
@@ -6475,7 +6771,7 @@
         <v>208784.2053</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>246</v>
       </c>
@@ -6510,19 +6806,19 @@
         <v>33</v>
       </c>
       <c r="AB90">
-        <v>39.99009</v>
+        <v>39.990090000000002</v>
       </c>
       <c r="AC90">
-        <v>128.0485</v>
+        <v>128.04849999999999</v>
       </c>
       <c r="AD90">
         <v>236799</v>
       </c>
       <c r="AE90">
-        <v>236798.6621</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>236798.66209999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -6557,7 +6853,7 @@
         <v>33</v>
       </c>
       <c r="AB91">
-        <v>12.9676</v>
+        <v>12.967599999999999</v>
       </c>
       <c r="AC91">
         <v>100.512</v>
@@ -6569,7 +6865,7 @@
         <v>812462.5612</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>250</v>
       </c>
@@ -6598,19 +6894,19 @@
         <v>33</v>
       </c>
       <c r="AB92">
-        <v>-0.04663</v>
+        <v>-4.6629999999999998E-2</v>
       </c>
       <c r="AC92">
-        <v>-90.83238</v>
+        <v>-90.832380000000001</v>
       </c>
       <c r="AD92">
         <v>849473</v>
       </c>
       <c r="AE92">
-        <v>849472.6397000002</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>849472.63970000017</v>
+      </c>
+    </row>
+    <row r="93" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>251</v>
       </c>
@@ -6645,7 +6941,7 @@
         <v>33</v>
       </c>
       <c r="AB93">
-        <v>-9.626659999999999</v>
+        <v>-9.6266599999999993</v>
       </c>
       <c r="AC93">
         <v>126.71271</v>
@@ -6654,10 +6950,10 @@
         <v>89660</v>
       </c>
       <c r="AE93">
-        <v>89659.78376999999</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>89659.783769999995</v>
+      </c>
+    </row>
+    <row r="94" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>253</v>
       </c>
@@ -6692,19 +6988,19 @@
         <v>33</v>
       </c>
       <c r="AB94">
-        <v>-3.73182</v>
+        <v>-3.7318199999999999</v>
       </c>
       <c r="AC94">
-        <v>-172.45394</v>
+        <v>-172.45393999999999</v>
       </c>
       <c r="AD94">
         <v>745823</v>
       </c>
       <c r="AE94">
-        <v>745823.1723</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>745823.17229999998</v>
+      </c>
+    </row>
+    <row r="95" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>254</v>
       </c>
@@ -6763,7 +7059,7 @@
         <v>33</v>
       </c>
       <c r="AB95">
-        <v>48.3072</v>
+        <v>48.307200000000002</v>
       </c>
       <c r="AC95">
         <v>31.7865</v>
@@ -6772,10 +7068,10 @@
         <v>734668</v>
       </c>
       <c r="AE95">
-        <v>734668.3492000002</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>734668.34920000017</v>
+      </c>
+    </row>
+    <row r="96" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>64</v>
       </c>
@@ -6810,19 +7106,19 @@
         <v>33</v>
       </c>
       <c r="AB96">
-        <v>46.37145</v>
+        <v>46.371450000000003</v>
       </c>
       <c r="AC96">
-        <v>0.8105599999999999</v>
+        <v>0.81055999999999995</v>
       </c>
       <c r="AD96">
         <v>897522</v>
       </c>
       <c r="AE96">
-        <v>897522.0351</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>897522.03509999998</v>
+      </c>
+    </row>
+    <row r="97" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>256</v>
       </c>
@@ -6857,7 +7153,7 @@
         <v>33</v>
       </c>
       <c r="AB97">
-        <v>-22.75567</v>
+        <v>-22.755669999999999</v>
       </c>
       <c r="AC97">
         <v>15.2067</v>
@@ -6866,10 +7162,10 @@
         <v>1386405</v>
       </c>
       <c r="AE97">
-        <v>1386405.326</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>1386405.3259999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>258</v>
       </c>
@@ -6898,19 +7194,19 @@
         <v>33</v>
       </c>
       <c r="AB98">
-        <v>38.47507</v>
+        <v>38.475070000000002</v>
       </c>
       <c r="AC98">
-        <v>-27.97434</v>
+        <v>-27.974340000000002</v>
       </c>
       <c r="AD98">
         <v>962788</v>
       </c>
       <c r="AE98">
-        <v>962788.3495</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>962788.34950000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>54</v>
       </c>
@@ -6945,10 +7241,10 @@
         <v>33</v>
       </c>
       <c r="AB99">
-        <v>56.09381</v>
+        <v>56.093809999999998</v>
       </c>
       <c r="AC99">
-        <v>9.450469999999999</v>
+        <v>9.4504699999999993</v>
       </c>
       <c r="AD99">
         <v>147744</v>
@@ -6957,7 +7253,7 @@
         <v>147744.0325</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>261</v>
       </c>
@@ -6992,19 +7288,19 @@
         <v>33</v>
       </c>
       <c r="AB100">
-        <v>16.75109</v>
+        <v>16.751090000000001</v>
       </c>
       <c r="AC100">
-        <v>-169.50612</v>
+        <v>-169.50612000000001</v>
       </c>
       <c r="AD100">
         <v>442448</v>
       </c>
       <c r="AE100">
-        <v>442448.3936</v>
-      </c>
-    </row>
-    <row r="101">
+        <v>442448.39360000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>262</v>
       </c>
@@ -7036,16 +7332,16 @@
         <v>28.36674</v>
       </c>
       <c r="AC101">
-        <v>-17.58171</v>
+        <v>-17.581710000000001</v>
       </c>
       <c r="AD101">
         <v>453419</v>
       </c>
       <c r="AE101">
-        <v>453419.4586</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>453419.45860000001</v>
+      </c>
+    </row>
+    <row r="102" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>263</v>
       </c>
@@ -7104,19 +7400,19 @@
         <v>56</v>
       </c>
       <c r="AB102">
-        <v>45.4977</v>
+        <v>45.497700000000002</v>
       </c>
       <c r="AC102">
-        <v>13.30933</v>
+        <v>13.309329999999999</v>
       </c>
       <c r="AD102">
         <v>98</v>
       </c>
       <c r="AE102">
-        <v>98.31893423</v>
-      </c>
-    </row>
-    <row r="103">
+        <v>98.318934229999996</v>
+      </c>
+    </row>
+    <row r="103" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>268</v>
       </c>
@@ -7151,19 +7447,19 @@
         <v>33</v>
       </c>
       <c r="AB103">
-        <v>55.37716</v>
+        <v>55.377160000000003</v>
       </c>
       <c r="AC103">
-        <v>23.56012</v>
+        <v>23.560120000000001</v>
       </c>
       <c r="AD103">
         <v>71779</v>
       </c>
       <c r="AE103">
-        <v>71779.08695</v>
-      </c>
-    </row>
-    <row r="104">
+        <v>71779.086949999997</v>
+      </c>
+    </row>
+    <row r="104" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>105</v>
       </c>
@@ -7222,19 +7518,19 @@
         <v>33</v>
       </c>
       <c r="AB104">
-        <v>21.63875</v>
+        <v>21.638750000000002</v>
       </c>
       <c r="AC104">
-        <v>118.92579</v>
+        <v>118.92579000000001</v>
       </c>
       <c r="AD104">
         <v>391613</v>
       </c>
       <c r="AE104">
-        <v>391613.4811</v>
-      </c>
-    </row>
-    <row r="105">
+        <v>391613.48109999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>270</v>
       </c>
@@ -7293,7 +7589,7 @@
         <v>56</v>
       </c>
       <c r="AB105">
-        <v>58.80998</v>
+        <v>58.809980000000003</v>
       </c>
       <c r="AC105">
         <v>10.50095</v>
@@ -7302,10 +7598,10 @@
         <v>140</v>
       </c>
       <c r="AE105">
-        <v>140.2085364</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>140.20853640000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>273</v>
       </c>
@@ -7367,16 +7663,16 @@
         <v>-9.53965</v>
       </c>
       <c r="AC106">
-        <v>142.40882</v>
+        <v>142.40881999999999</v>
       </c>
       <c r="AD106">
         <v>2621</v>
       </c>
       <c r="AE106">
-        <v>2620.850591</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>2620.8505909999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>276</v>
       </c>
@@ -7411,10 +7707,10 @@
         <v>33</v>
       </c>
       <c r="AB107">
-        <v>-19.52276</v>
+        <v>-19.522760000000002</v>
       </c>
       <c r="AC107">
-        <v>-169.33182</v>
+        <v>-169.33181999999999</v>
       </c>
       <c r="AD107">
         <v>318407</v>
@@ -7423,7 +7719,7 @@
         <v>318407.1764</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>278</v>
       </c>
@@ -7458,19 +7754,19 @@
         <v>33</v>
       </c>
       <c r="AB108">
-        <v>17.94583</v>
+        <v>17.945830000000001</v>
       </c>
       <c r="AC108">
-        <v>-63.11828</v>
+        <v>-63.118279999999999</v>
       </c>
       <c r="AD108">
         <v>505</v>
       </c>
       <c r="AE108">
-        <v>504.6385051</v>
-      </c>
-    </row>
-    <row r="109">
+        <v>504.63850509999997</v>
+      </c>
+    </row>
+    <row r="109" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>282</v>
       </c>
@@ -7505,19 +7801,19 @@
         <v>33</v>
       </c>
       <c r="AB109">
-        <v>17.82148</v>
+        <v>17.821480000000001</v>
       </c>
       <c r="AC109">
-        <v>-66.76937</v>
+        <v>-66.769369999999995</v>
       </c>
       <c r="AD109">
         <v>163631</v>
       </c>
       <c r="AE109">
-        <v>163631.3489</v>
-      </c>
-    </row>
-    <row r="110">
+        <v>163631.34890000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>284</v>
       </c>
@@ -7564,19 +7860,19 @@
         <v>39</v>
       </c>
       <c r="AB110">
-        <v>35.23416</v>
+        <v>35.234160000000003</v>
       </c>
       <c r="AC110">
-        <v>-3.87872</v>
+        <v>-3.8787199999999999</v>
       </c>
       <c r="AD110">
         <v>14</v>
       </c>
       <c r="AE110">
-        <v>14.10069656</v>
-      </c>
-    </row>
-    <row r="111">
+        <v>14.100696559999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>285</v>
       </c>
@@ -7611,19 +7907,19 @@
         <v>33</v>
       </c>
       <c r="AB111">
-        <v>16.99792</v>
+        <v>16.997920000000001</v>
       </c>
       <c r="AC111">
-        <v>-62.90018</v>
+        <v>-62.900179999999999</v>
       </c>
       <c r="AD111">
         <v>9769</v>
       </c>
       <c r="AE111">
-        <v>9768.631729000001</v>
-      </c>
-    </row>
-    <row r="112">
+        <v>9768.6317290000006</v>
+      </c>
+    </row>
+    <row r="112" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>287</v>
       </c>
@@ -7658,7 +7954,7 @@
         <v>33</v>
       </c>
       <c r="AB112">
-        <v>-0.91398</v>
+        <v>-0.91398000000000001</v>
       </c>
       <c r="AC112">
         <v>-160.46838</v>
@@ -7670,7 +7966,7 @@
         <v>323192.6875</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>288</v>
       </c>
@@ -7735,19 +8031,19 @@
         <v>39</v>
       </c>
       <c r="AB113">
-        <v>-15.71127</v>
+        <v>-15.711270000000001</v>
       </c>
       <c r="AC113">
-        <v>54.67305</v>
+        <v>54.673050000000003</v>
       </c>
       <c r="AD113">
         <v>274562</v>
       </c>
       <c r="AE113">
-        <v>274562.3249</v>
-      </c>
-    </row>
-    <row r="114">
+        <v>274562.32490000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>294</v>
       </c>
@@ -7782,10 +8078,10 @@
         <v>33</v>
       </c>
       <c r="AB114">
-        <v>-23.53637</v>
+        <v>-23.536370000000002</v>
       </c>
       <c r="AC114">
-        <v>40.10937</v>
+        <v>40.109369999999998</v>
       </c>
       <c r="AD114">
         <v>127986</v>
@@ -7794,7 +8090,7 @@
         <v>127985.5126</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>296</v>
       </c>
@@ -7829,7 +8125,7 @@
         <v>33</v>
       </c>
       <c r="AB115">
-        <v>35.3173</v>
+        <v>35.317300000000003</v>
       </c>
       <c r="AC115">
         <v>15.10683</v>
@@ -7838,10 +8134,10 @@
         <v>53247</v>
       </c>
       <c r="AE115">
-        <v>53247.41011</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>53247.410109999997</v>
+      </c>
+    </row>
+    <row r="116" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>298</v>
       </c>
@@ -7876,10 +8172,10 @@
         <v>33</v>
       </c>
       <c r="AB116">
-        <v>17.37777</v>
+        <v>17.377770000000002</v>
       </c>
       <c r="AC116">
-        <v>-63.6013</v>
+        <v>-63.601300000000002</v>
       </c>
       <c r="AD116">
         <v>9502</v>
@@ -7888,7 +8184,7 @@
         <v>9501.573907</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>168</v>
       </c>
@@ -7923,19 +8219,19 @@
         <v>33</v>
       </c>
       <c r="AB117">
-        <v>-40.31881</v>
+        <v>-40.318809999999999</v>
       </c>
       <c r="AC117">
-        <v>-74.67068999999999</v>
+        <v>-74.670689999999993</v>
       </c>
       <c r="AD117">
         <v>3244212</v>
       </c>
       <c r="AE117">
-        <v>3244211.698</v>
-      </c>
-    </row>
-    <row r="118">
+        <v>3244211.6979999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>144</v>
       </c>
@@ -7970,7 +8266,7 @@
         <v>33</v>
       </c>
       <c r="AB118">
-        <v>-31.16021</v>
+        <v>-31.160209999999999</v>
       </c>
       <c r="AC118">
         <v>24.77862</v>
@@ -7979,10 +8275,10 @@
         <v>2292218</v>
       </c>
       <c r="AE118">
-        <v>2292218.116</v>
-      </c>
-    </row>
-    <row r="119">
+        <v>2292218.1159999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>300</v>
       </c>
@@ -8017,19 +8313,19 @@
         <v>33</v>
       </c>
       <c r="AB119">
-        <v>5.61301</v>
+        <v>5.6130100000000001</v>
       </c>
       <c r="AC119">
-        <v>-52.32892</v>
+        <v>-52.328919999999997</v>
       </c>
       <c r="AD119">
         <v>214504</v>
       </c>
       <c r="AE119">
-        <v>214504.1101</v>
-      </c>
-    </row>
-    <row r="120">
+        <v>214504.11009999999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>302</v>
       </c>
@@ -8064,7 +8360,7 @@
         <v>33</v>
       </c>
       <c r="AB120">
-        <v>49.58068</v>
+        <v>49.580680000000001</v>
       </c>
       <c r="AC120">
         <v>-2.49607</v>
@@ -8073,10 +8369,10 @@
         <v>3769</v>
       </c>
       <c r="AE120">
-        <v>3768.532398</v>
-      </c>
-    </row>
-    <row r="121">
+        <v>3768.5323979999998</v>
+      </c>
+    </row>
+    <row r="121" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>236</v>
       </c>
@@ -8111,19 +8407,19 @@
         <v>33</v>
       </c>
       <c r="AB121">
-        <v>-16.57803</v>
+        <v>-16.578029999999998</v>
       </c>
       <c r="AC121">
-        <v>168.54132</v>
+        <v>168.54132000000001</v>
       </c>
       <c r="AD121">
         <v>638186</v>
       </c>
       <c r="AE121">
-        <v>638186.3255</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>638186.32550000004</v>
+      </c>
+    </row>
+    <row r="122" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>304</v>
       </c>
@@ -8155,19 +8451,19 @@
         <v>59</v>
       </c>
       <c r="AB122">
-        <v>40.2948</v>
+        <v>40.294800000000002</v>
       </c>
       <c r="AC122">
-        <v>44.93935</v>
+        <v>44.939349999999997</v>
       </c>
       <c r="AD122">
         <v>29733</v>
       </c>
       <c r="AE122">
-        <v>29732.93033</v>
-      </c>
-    </row>
-    <row r="123">
+        <v>29732.930329999999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>131</v>
       </c>
@@ -8202,10 +8498,10 @@
         <v>33</v>
       </c>
       <c r="AB123">
-        <v>32.05808</v>
+        <v>32.058079999999997</v>
       </c>
       <c r="AC123">
-        <v>34.48299</v>
+        <v>34.482990000000001</v>
       </c>
       <c r="AD123">
         <v>46693</v>
@@ -8214,7 +8510,7 @@
         <v>46692.92813</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>306</v>
       </c>
@@ -8246,19 +8542,19 @@
         <v>59</v>
       </c>
       <c r="AB124">
-        <v>-16.71004</v>
+        <v>-16.710039999999999</v>
       </c>
       <c r="AC124">
-        <v>-64.66432</v>
+        <v>-64.664320000000004</v>
       </c>
       <c r="AD124">
         <v>1082641</v>
       </c>
       <c r="AE124">
-        <v>1082640.856</v>
-      </c>
-    </row>
-    <row r="125">
+        <v>1082640.8559999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>308</v>
       </c>
@@ -8287,19 +8583,19 @@
         <v>33</v>
       </c>
       <c r="AB125">
-        <v>-6.55595</v>
+        <v>-6.5559500000000002</v>
       </c>
       <c r="AC125">
-        <v>71.99388999999999</v>
+        <v>71.993889999999993</v>
       </c>
       <c r="AD125">
         <v>647738</v>
       </c>
       <c r="AE125">
-        <v>647738.231</v>
-      </c>
-    </row>
-    <row r="126">
+        <v>647738.23100000003</v>
+      </c>
+    </row>
+    <row r="126" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>309</v>
       </c>
@@ -8334,10 +8630,10 @@
         <v>33</v>
       </c>
       <c r="AB126">
-        <v>5.47527</v>
+        <v>5.4752700000000001</v>
       </c>
       <c r="AC126">
-        <v>47.35015</v>
+        <v>47.350149999999999</v>
       </c>
       <c r="AD126">
         <v>1454124</v>
@@ -8346,7 +8642,7 @@
         <v>1454124.33</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>311</v>
       </c>
@@ -8381,19 +8677,19 @@
         <v>33</v>
       </c>
       <c r="AB127">
-        <v>17.34052</v>
+        <v>17.340520000000001</v>
       </c>
       <c r="AC127">
-        <v>-63.12824</v>
+        <v>-63.128239999999998</v>
       </c>
       <c r="AD127">
         <v>2199</v>
       </c>
       <c r="AE127">
-        <v>2199.099395</v>
-      </c>
-    </row>
-    <row r="128">
+        <v>2199.0993950000002</v>
+      </c>
+    </row>
+    <row r="128" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>312</v>
       </c>
@@ -8428,16 +8724,16 @@
         <v>1.27918</v>
       </c>
       <c r="AC128">
-        <v>32.38997</v>
+        <v>32.389969999999998</v>
       </c>
       <c r="AD128">
         <v>241519</v>
       </c>
       <c r="AE128">
-        <v>241519.178</v>
-      </c>
-    </row>
-    <row r="129">
+        <v>241519.17800000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>314</v>
       </c>
@@ -8469,7 +8765,7 @@
         <v>59</v>
       </c>
       <c r="AB129">
-        <v>41.60059</v>
+        <v>41.600589999999997</v>
       </c>
       <c r="AC129">
         <v>21.69875</v>
@@ -8481,7 +8777,7 @@
         <v>25437.19787</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>316</v>
       </c>
@@ -8549,10 +8845,10 @@
         <v>67</v>
       </c>
       <c r="AE130">
-        <v>67.15753871</v>
-      </c>
-    </row>
-    <row r="131">
+        <v>67.157538709999997</v>
+      </c>
+    </row>
+    <row r="131" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>96</v>
       </c>
@@ -8587,10 +8883,10 @@
         <v>33</v>
       </c>
       <c r="AB131">
-        <v>-10.86316</v>
+        <v>-10.863160000000001</v>
       </c>
       <c r="AC131">
-        <v>-49.30546</v>
+        <v>-49.305459999999997</v>
       </c>
       <c r="AD131">
         <v>11678267</v>
@@ -8599,7 +8895,7 @@
         <v>11678266.58</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>319</v>
       </c>
@@ -8646,7 +8942,7 @@
         <v>250790.027</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>321</v>
       </c>
@@ -8678,16 +8974,16 @@
         <v>14.30378</v>
       </c>
       <c r="AC133">
-        <v>-81.16149</v>
+        <v>-81.161490000000001</v>
       </c>
       <c r="AD133">
         <v>4009</v>
       </c>
       <c r="AE133">
-        <v>4008.865682</v>
-      </c>
-    </row>
-    <row r="134">
+        <v>4008.8656820000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>325</v>
       </c>
@@ -8719,10 +9015,10 @@
         <v>59</v>
       </c>
       <c r="AB134">
-        <v>41.46415</v>
+        <v>41.464149999999997</v>
       </c>
       <c r="AC134">
-        <v>74.55450999999999</v>
+        <v>74.554509999999993</v>
       </c>
       <c r="AD134">
         <v>199638</v>
@@ -8731,7 +9027,7 @@
         <v>199637.6734</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>327</v>
       </c>
@@ -8760,19 +9056,19 @@
         <v>33</v>
       </c>
       <c r="AB135">
-        <v>24.01626</v>
+        <v>24.016259999999999</v>
       </c>
       <c r="AC135">
-        <v>-151.09216</v>
+        <v>-151.09216000000001</v>
       </c>
       <c r="AD135">
         <v>2491444</v>
       </c>
       <c r="AE135">
-        <v>2491444.428</v>
-      </c>
-    </row>
-    <row r="136">
+        <v>2491444.4279999998</v>
+      </c>
+    </row>
+    <row r="136" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>328</v>
       </c>
@@ -8810,16 +9106,16 @@
         <v>16.78811</v>
       </c>
       <c r="AC136">
-        <v>-59.88047</v>
+        <v>-59.880470000000003</v>
       </c>
       <c r="AD136">
         <v>92355</v>
       </c>
       <c r="AE136">
-        <v>92355.18888</v>
-      </c>
-    </row>
-    <row r="137">
+        <v>92355.188880000002</v>
+      </c>
+    </row>
+    <row r="137" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>330</v>
       </c>
@@ -8857,7 +9153,7 @@
         <v>-18.73237</v>
       </c>
       <c r="AC137">
-        <v>-144.00452</v>
+        <v>-144.00452000000001</v>
       </c>
       <c r="AD137">
         <v>4774878</v>
@@ -8866,7 +9162,7 @@
         <v>4774877.62</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>332</v>
       </c>
@@ -8925,10 +9221,10 @@
         <v>39</v>
       </c>
       <c r="AB138">
-        <v>36.08911</v>
+        <v>36.089109999999998</v>
       </c>
       <c r="AC138">
-        <v>-5.22177</v>
+        <v>-5.2217700000000002</v>
       </c>
       <c r="AD138">
         <v>395</v>
@@ -8937,7 +9233,7 @@
         <v>394.8886291</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>334</v>
       </c>
@@ -8972,19 +9268,19 @@
         <v>33</v>
       </c>
       <c r="AB139">
-        <v>63.97904</v>
+        <v>63.979039999999998</v>
       </c>
       <c r="AC139">
-        <v>25.44114</v>
+        <v>25.441140000000001</v>
       </c>
       <c r="AD139">
         <v>420076</v>
       </c>
       <c r="AE139">
-        <v>420076.1537</v>
-      </c>
-    </row>
-    <row r="140">
+        <v>420076.15370000002</v>
+      </c>
+    </row>
+    <row r="140" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>336</v>
       </c>
@@ -9019,19 +9315,19 @@
         <v>33</v>
       </c>
       <c r="AB140">
-        <v>35.03314</v>
+        <v>35.033140000000003</v>
       </c>
       <c r="AC140">
-        <v>38.34089</v>
+        <v>38.340890000000002</v>
       </c>
       <c r="AD140">
         <v>197868</v>
       </c>
       <c r="AE140">
-        <v>197867.8245</v>
-      </c>
-    </row>
-    <row r="141">
+        <v>197867.82449999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>338</v>
       </c>
@@ -9114,10 +9410,10 @@
         <v>39</v>
       </c>
       <c r="AB141">
-        <v>10.56539</v>
+        <v>10.565390000000001</v>
       </c>
       <c r="AC141">
-        <v>-57.88712</v>
+        <v>-57.887120000000003</v>
       </c>
       <c r="AD141">
         <v>3612</v>
@@ -9126,7 +9422,7 @@
         <v>3611.536364</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>50</v>
       </c>
@@ -9161,19 +9457,19 @@
         <v>33</v>
       </c>
       <c r="AB142">
-        <v>56.16188</v>
+        <v>56.161879999999996</v>
       </c>
       <c r="AC142">
-        <v>-3.95569</v>
+        <v>-3.9556900000000002</v>
       </c>
       <c r="AD142">
         <v>972473</v>
       </c>
       <c r="AE142">
-        <v>972473.4921</v>
-      </c>
-    </row>
-    <row r="143">
+        <v>972473.49210000003</v>
+      </c>
+    </row>
+    <row r="143" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>341</v>
       </c>
@@ -9208,7 +9504,7 @@
         <v>33</v>
       </c>
       <c r="AB143">
-        <v>-38.7618</v>
+        <v>-38.761800000000001</v>
       </c>
       <c r="AC143">
         <v>-11.20992</v>
@@ -9217,10 +9513,10 @@
         <v>758353</v>
       </c>
       <c r="AE143">
-        <v>758352.7671000002</v>
-      </c>
-    </row>
-    <row r="144">
+        <v>758352.76710000017</v>
+      </c>
+    </row>
+    <row r="144" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>343</v>
       </c>
@@ -9255,7 +9551,7 @@
         <v>33</v>
       </c>
       <c r="AB144">
-        <v>-11.24326</v>
+        <v>-11.243259999999999</v>
       </c>
       <c r="AC144">
         <v>105.36534</v>
@@ -9264,10 +9560,10 @@
         <v>328134</v>
       </c>
       <c r="AE144">
-        <v>328133.6411</v>
-      </c>
-    </row>
-    <row r="145">
+        <v>328133.64110000001</v>
+      </c>
+    </row>
+    <row r="145" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>345</v>
       </c>
@@ -9302,19 +9598,19 @@
         <v>33</v>
       </c>
       <c r="AB145">
-        <v>52.38821</v>
+        <v>52.388210000000001</v>
       </c>
       <c r="AC145">
-        <v>19.19902</v>
+        <v>19.199020000000001</v>
       </c>
       <c r="AD145">
         <v>342427</v>
       </c>
       <c r="AE145">
-        <v>342427.1866</v>
-      </c>
-    </row>
-    <row r="146">
+        <v>342427.18660000002</v>
+      </c>
+    </row>
+    <row r="146" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>114</v>
       </c>
@@ -9349,19 +9645,19 @@
         <v>33</v>
       </c>
       <c r="AB146">
-        <v>-1.21701</v>
+        <v>-1.2170099999999999</v>
       </c>
       <c r="AC146">
-        <v>-80.24720000000001</v>
+        <v>-80.247200000000007</v>
       </c>
       <c r="AD146">
         <v>484248</v>
       </c>
       <c r="AE146">
-        <v>484248.1905</v>
-      </c>
-    </row>
-    <row r="147">
+        <v>484248.19050000003</v>
+      </c>
+    </row>
+    <row r="147" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>347</v>
       </c>
@@ -9396,10 +9692,10 @@
         <v>33</v>
       </c>
       <c r="AB147">
-        <v>28.20256</v>
+        <v>28.202559999999998</v>
       </c>
       <c r="AC147">
-        <v>18.08707</v>
+        <v>18.087070000000001</v>
       </c>
       <c r="AD147">
         <v>1973738</v>
@@ -9408,7 +9704,7 @@
         <v>1973738.166</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>349</v>
       </c>
@@ -9443,7 +9739,7 @@
         <v>33</v>
       </c>
       <c r="AB148">
-        <v>-0.16944</v>
+        <v>-0.16944000000000001</v>
       </c>
       <c r="AC148">
         <v>38.57658</v>
@@ -9452,10 +9748,10 @@
         <v>707485</v>
       </c>
       <c r="AE148">
-        <v>707484.6591</v>
-      </c>
-    </row>
-    <row r="149">
+        <v>707484.65910000005</v>
+      </c>
+    </row>
+    <row r="149" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>351</v>
       </c>
@@ -9490,10 +9786,10 @@
         <v>33</v>
       </c>
       <c r="AB149">
-        <v>-13.30647</v>
+        <v>-13.306469999999999</v>
       </c>
       <c r="AC149">
-        <v>-172.74125</v>
+        <v>-172.74125000000001</v>
       </c>
       <c r="AD149">
         <v>133334</v>
@@ -9502,7 +9798,7 @@
         <v>133333.9137</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>353</v>
       </c>
@@ -9540,7 +9836,7 @@
         <v>12.18533</v>
       </c>
       <c r="AC150">
-        <v>-89.58804000000001</v>
+        <v>-89.588040000000007</v>
       </c>
       <c r="AD150">
         <v>115630</v>
@@ -9549,7 +9845,7 @@
         <v>115630.1488</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>355</v>
       </c>
@@ -9584,19 +9880,19 @@
         <v>33</v>
       </c>
       <c r="AB151">
-        <v>50.72703</v>
+        <v>50.727029999999999</v>
       </c>
       <c r="AC151">
-        <v>4.45732</v>
+        <v>4.4573200000000002</v>
       </c>
       <c r="AD151">
         <v>34122</v>
       </c>
       <c r="AE151">
-        <v>34122.1657</v>
-      </c>
-    </row>
-    <row r="152">
+        <v>34122.165699999998</v>
+      </c>
+    </row>
+    <row r="152" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>357</v>
       </c>
@@ -9652,10 +9948,10 @@
         <v>39</v>
       </c>
       <c r="AB152">
-        <v>18.33817</v>
+        <v>18.338170000000002</v>
       </c>
       <c r="AC152">
-        <v>-75.18366</v>
+        <v>-75.183660000000003</v>
       </c>
       <c r="AD152">
         <v>13895</v>
@@ -9664,7 +9960,7 @@
         <v>13895.46578</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>358</v>
       </c>
@@ -9750,16 +10046,16 @@
         <v>15.05334</v>
       </c>
       <c r="AC153">
-        <v>-71.09014999999999</v>
+        <v>-71.090149999999994</v>
       </c>
       <c r="AD153">
         <v>869</v>
       </c>
       <c r="AE153">
-        <v>868.704255</v>
-      </c>
-    </row>
-    <row r="154">
+        <v>868.70425499999999</v>
+      </c>
+    </row>
+    <row r="154" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>290</v>
       </c>
@@ -9797,16 +10093,16 @@
         <v>-20.40898</v>
       </c>
       <c r="AC154">
-        <v>47.07263</v>
+        <v>47.072629999999997</v>
       </c>
       <c r="AD154">
         <v>1786627</v>
       </c>
       <c r="AE154">
-        <v>1786627.146</v>
-      </c>
-    </row>
-    <row r="155">
+        <v>1786627.1459999999</v>
+      </c>
+    </row>
+    <row r="155" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>361</v>
       </c>
@@ -9862,7 +10158,7 @@
         <v>-11.61806</v>
       </c>
       <c r="AC155">
-        <v>47.09707</v>
+        <v>47.097070000000002</v>
       </c>
       <c r="AD155">
         <v>43538</v>
@@ -9871,7 +10167,7 @@
         <v>43537.67295</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>362</v>
       </c>
@@ -9903,19 +10199,19 @@
         <v>59</v>
       </c>
       <c r="AB156">
-        <v>49.77724</v>
+        <v>49.777239999999999</v>
       </c>
       <c r="AC156">
-        <v>6.09238</v>
+        <v>6.0923800000000004</v>
       </c>
       <c r="AD156">
         <v>2595</v>
       </c>
       <c r="AE156">
-        <v>2595.470758</v>
-      </c>
-    </row>
-    <row r="157">
+        <v>2595.4707579999999</v>
+      </c>
+    </row>
+    <row r="157" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>364</v>
       </c>
@@ -9950,19 +10246,19 @@
         <v>33</v>
       </c>
       <c r="AB157">
-        <v>20.01639</v>
+        <v>20.016390000000001</v>
       </c>
       <c r="AC157">
-        <v>-62.54376</v>
+        <v>-62.543759999999999</v>
       </c>
       <c r="AD157">
         <v>90247</v>
       </c>
       <c r="AE157">
-        <v>90247.35378</v>
-      </c>
-    </row>
-    <row r="158">
+        <v>90247.353780000005</v>
+      </c>
+    </row>
+    <row r="158" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>366</v>
       </c>
@@ -9997,10 +10293,10 @@
         <v>33</v>
       </c>
       <c r="AB158">
-        <v>12.69987</v>
+        <v>12.699870000000001</v>
       </c>
       <c r="AC158">
-        <v>-68.36807</v>
+        <v>-68.368070000000003</v>
       </c>
       <c r="AD158">
         <v>13290</v>
@@ -10009,7 +10305,7 @@
         <v>13290.22322</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>264</v>
       </c>
@@ -10047,7 +10343,7 @@
         <v>44.2575</v>
       </c>
       <c r="AC159">
-        <v>16.03628</v>
+        <v>16.036280000000001</v>
       </c>
       <c r="AD159">
         <v>112170</v>
@@ -10056,7 +10352,7 @@
         <v>112170.1033</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>367</v>
       </c>
@@ -10091,19 +10387,19 @@
         <v>33</v>
       </c>
       <c r="AB160">
-        <v>7.00015</v>
+        <v>7.0001499999999997</v>
       </c>
       <c r="AC160">
-        <v>-86.31941999999999</v>
+        <v>-86.319419999999994</v>
       </c>
       <c r="AD160">
         <v>632868</v>
       </c>
       <c r="AE160">
-        <v>632867.9047</v>
-      </c>
-    </row>
-    <row r="161">
+        <v>632867.90469999996</v>
+      </c>
+    </row>
+    <row r="161" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>369</v>
       </c>
@@ -10135,10 +10431,10 @@
         <v>59</v>
       </c>
       <c r="AB161">
-        <v>-29.58395</v>
+        <v>-29.583950000000002</v>
       </c>
       <c r="AC161">
-        <v>28.24612</v>
+        <v>28.246120000000001</v>
       </c>
       <c r="AD161">
         <v>30562</v>
@@ -10147,7 +10443,7 @@
         <v>30561.65539</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>371</v>
       </c>
@@ -10179,7 +10475,7 @@
         <v>59</v>
       </c>
       <c r="AB162">
-        <v>48.70746</v>
+        <v>48.707459999999998</v>
       </c>
       <c r="AC162">
         <v>19.48507</v>
@@ -10188,10 +10484,10 @@
         <v>49038</v>
       </c>
       <c r="AE162">
-        <v>49037.64322</v>
-      </c>
-    </row>
-    <row r="163">
+        <v>49037.643219999998</v>
+      </c>
+    </row>
+    <row r="163" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>45</v>
       </c>
@@ -10226,19 +10522,19 @@
         <v>33</v>
       </c>
       <c r="AB163">
-        <v>35.80488</v>
+        <v>35.804879999999997</v>
       </c>
       <c r="AC163">
-        <v>105.06602</v>
+        <v>105.06601999999999</v>
       </c>
       <c r="AD163">
         <v>10340834</v>
       </c>
       <c r="AE163">
-        <v>10340834.12</v>
-      </c>
-    </row>
-    <row r="164">
+        <v>10340834.119999999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>373</v>
       </c>
@@ -10300,16 +10596,16 @@
         <v>18.70111</v>
       </c>
       <c r="AC164">
-        <v>-83.94222000000001</v>
+        <v>-83.942220000000006</v>
       </c>
       <c r="AD164">
         <v>2075</v>
       </c>
       <c r="AE164">
-        <v>2075.281021</v>
-      </c>
-    </row>
-    <row r="165">
+        <v>2075.2810209999998</v>
+      </c>
+    </row>
+    <row r="165" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>376</v>
       </c>
@@ -10344,10 +10640,10 @@
         <v>33</v>
       </c>
       <c r="AB165">
-        <v>34.53785</v>
+        <v>34.537849999999999</v>
       </c>
       <c r="AC165">
-        <v>32.68645</v>
+        <v>32.686450000000001</v>
       </c>
       <c r="AD165">
         <v>107717</v>
@@ -10356,7 +10652,7 @@
         <v>107717.1685</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>374</v>
       </c>
@@ -10391,19 +10687,19 @@
         <v>33</v>
       </c>
       <c r="AB166">
-        <v>16.18527</v>
+        <v>16.185269999999999</v>
       </c>
       <c r="AC166">
-        <v>-84.81067</v>
+        <v>-84.810670000000002</v>
       </c>
       <c r="AD166">
         <v>320588</v>
       </c>
       <c r="AE166">
-        <v>320588.1623000001</v>
-      </c>
-    </row>
-    <row r="167">
+        <v>320588.16230000008</v>
+      </c>
+    </row>
+    <row r="167" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>378</v>
       </c>
@@ -10438,16 +10734,16 @@
         <v>-26.5657</v>
       </c>
       <c r="AC167">
-        <v>31.49955</v>
+        <v>31.499549999999999</v>
       </c>
       <c r="AD167">
         <v>17367</v>
       </c>
       <c r="AE167">
-        <v>17367.387</v>
-      </c>
-    </row>
-    <row r="168">
+        <v>17367.386999999999</v>
+      </c>
+    </row>
+    <row r="168" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>380</v>
       </c>
@@ -10482,10 +10778,10 @@
         <v>33</v>
       </c>
       <c r="AB168">
-        <v>16.73015</v>
+        <v>16.730149999999998</v>
       </c>
       <c r="AC168">
-        <v>-77.29169</v>
+        <v>-77.291690000000003</v>
       </c>
       <c r="AD168">
         <v>267912</v>
@@ -10494,7 +10790,7 @@
         <v>267911.9523</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>382</v>
       </c>
@@ -10529,10 +10825,10 @@
         <v>33</v>
       </c>
       <c r="AB169">
-        <v>17.26167</v>
+        <v>17.261669999999999</v>
       </c>
       <c r="AC169">
-        <v>-64.92319999999999</v>
+        <v>-64.923199999999994</v>
       </c>
       <c r="AD169">
         <v>38636</v>
@@ -10541,7 +10837,7 @@
         <v>38636.04954</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>384</v>
       </c>
@@ -10576,7 +10872,7 @@
         <v>33</v>
       </c>
       <c r="AB170">
-        <v>39.43465</v>
+        <v>39.434649999999998</v>
       </c>
       <c r="AC170">
         <v>34.67266</v>
@@ -10588,7 +10884,7 @@
         <v>1042327.031</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>386</v>
       </c>
@@ -10626,16 +10922,16 @@
         <v>-48.88353</v>
       </c>
       <c r="AC171">
-        <v>68.98137</v>
+        <v>68.981369999999998</v>
       </c>
       <c r="AD171">
         <v>558170</v>
       </c>
       <c r="AE171">
-        <v>558169.7229000002</v>
-      </c>
-    </row>
-    <row r="172">
+        <v>558169.72290000017</v>
+      </c>
+    </row>
+    <row r="172" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>387</v>
       </c>
@@ -10673,16 +10969,16 @@
         <v>26.30894</v>
       </c>
       <c r="AC172">
-        <v>50.69234</v>
+        <v>50.692340000000002</v>
       </c>
       <c r="AD172">
         <v>8272</v>
       </c>
       <c r="AE172">
-        <v>8272.090040999999</v>
-      </c>
-    </row>
-    <row r="173">
+        <v>8272.0900409999995</v>
+      </c>
+    </row>
+    <row r="173" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>339</v>
       </c>
@@ -10717,19 +11013,19 @@
         <v>33</v>
       </c>
       <c r="AB173">
-        <v>10.92738</v>
+        <v>10.927379999999999</v>
       </c>
       <c r="AC173">
-        <v>-60.06508</v>
+        <v>-60.065080000000002</v>
       </c>
       <c r="AD173">
         <v>81719</v>
       </c>
       <c r="AE173">
-        <v>81719.32345</v>
-      </c>
-    </row>
-    <row r="174">
+        <v>81719.323449999996</v>
+      </c>
+    </row>
+    <row r="174" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>389</v>
       </c>
@@ -10761,10 +11057,10 @@
         <v>59</v>
       </c>
       <c r="AB174">
-        <v>-13.21296</v>
+        <v>-13.212960000000001</v>
       </c>
       <c r="AC174">
-        <v>34.30139</v>
+        <v>34.301389999999998</v>
       </c>
       <c r="AD174">
         <v>118501</v>
@@ -10773,7 +11069,7 @@
         <v>118501.0583</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>391</v>
       </c>
@@ -10832,7 +11128,7 @@
         <v>39</v>
       </c>
       <c r="AB175">
-        <v>72.03395</v>
+        <v>72.033950000000004</v>
       </c>
       <c r="AC175">
         <v>-139.852</v>
@@ -10841,10 +11137,10 @@
         <v>24772</v>
       </c>
       <c r="AE175">
-        <v>24772.31068</v>
-      </c>
-    </row>
-    <row r="176">
+        <v>24772.310679999999</v>
+      </c>
+    </row>
+    <row r="176" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>394</v>
       </c>
@@ -10879,7 +11175,7 @@
         <v>33</v>
       </c>
       <c r="AB176">
-        <v>15.55468</v>
+        <v>15.554679999999999</v>
       </c>
       <c r="AC176">
         <v>39.52946</v>
@@ -10888,10 +11184,10 @@
         <v>199286</v>
       </c>
       <c r="AE176">
-        <v>199286.1331</v>
-      </c>
-    </row>
-    <row r="177">
+        <v>199286.13310000001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>396</v>
       </c>
@@ -10929,16 +11225,16 @@
         <v>15.49577</v>
       </c>
       <c r="AC177">
-        <v>-60.73732</v>
+        <v>-60.737319999999997</v>
       </c>
       <c r="AD177">
         <v>29307</v>
       </c>
       <c r="AE177">
-        <v>29307.45227</v>
-      </c>
-    </row>
-    <row r="178">
+        <v>29307.452270000002</v>
+      </c>
+    </row>
+    <row r="178" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>259</v>
       </c>
@@ -10976,16 +11272,16 @@
         <v>38.62323</v>
       </c>
       <c r="AC178">
-        <v>-10.26364</v>
+        <v>-10.263640000000001</v>
       </c>
       <c r="AD178">
         <v>404204</v>
       </c>
       <c r="AE178">
-        <v>404204.1673</v>
-      </c>
-    </row>
-    <row r="179">
+        <v>404204.16729999997</v>
+      </c>
+    </row>
+    <row r="179" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>398</v>
       </c>
@@ -11020,19 +11316,19 @@
         <v>33</v>
       </c>
       <c r="AB179">
-        <v>37.06672</v>
+        <v>37.066719999999997</v>
       </c>
       <c r="AC179">
-        <v>23.72328</v>
+        <v>23.723279999999999</v>
       </c>
       <c r="AD179">
         <v>615356</v>
       </c>
       <c r="AE179">
-        <v>615356.1361999999</v>
-      </c>
-    </row>
-    <row r="180">
+        <v>615356.13619999995</v>
+      </c>
+    </row>
+    <row r="180" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>400</v>
       </c>
@@ -11115,7 +11411,7 @@
         <v>39</v>
       </c>
       <c r="AB180">
-        <v>24.69243</v>
+        <v>24.692430000000002</v>
       </c>
       <c r="AC180">
         <v>51.59986</v>
@@ -11127,7 +11423,7 @@
         <v>125.7368598</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>403</v>
       </c>
@@ -11186,19 +11482,19 @@
         <v>56</v>
       </c>
       <c r="AB181">
-        <v>45.25417</v>
+        <v>45.254170000000002</v>
       </c>
       <c r="AC181">
-        <v>-5.33333</v>
+        <v>-5.3333300000000001</v>
       </c>
       <c r="AD181">
         <v>2859</v>
       </c>
       <c r="AE181">
-        <v>2859.492199</v>
-      </c>
-    </row>
-    <row r="182">
+        <v>2859.4921989999998</v>
+      </c>
+    </row>
+    <row r="182" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>404</v>
       </c>
@@ -11227,19 +11523,19 @@
         <v>33</v>
       </c>
       <c r="AB182">
-        <v>33.17225</v>
+        <v>33.172249999999998</v>
       </c>
       <c r="AC182">
-        <v>-16.81115</v>
+        <v>-16.811150000000001</v>
       </c>
       <c r="AD182">
         <v>453616</v>
       </c>
       <c r="AE182">
-        <v>453615.7185</v>
-      </c>
-    </row>
-    <row r="183">
+        <v>453615.71850000002</v>
+      </c>
+    </row>
+    <row r="183" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>405</v>
       </c>
@@ -11274,19 +11570,19 @@
         <v>33</v>
       </c>
       <c r="AB183">
-        <v>49.1309</v>
+        <v>49.130899999999997</v>
       </c>
       <c r="AC183">
-        <v>-2.1902</v>
+        <v>-2.1901999999999999</v>
       </c>
       <c r="AD183">
         <v>2457</v>
       </c>
       <c r="AE183">
-        <v>2456.817384</v>
-      </c>
-    </row>
-    <row r="184">
+        <v>2456.8173839999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>407</v>
       </c>
@@ -11324,16 +11620,16 @@
         <v>13.14611</v>
       </c>
       <c r="AC184">
-        <v>-68.97176</v>
+        <v>-68.971760000000003</v>
       </c>
       <c r="AD184">
         <v>25838</v>
       </c>
       <c r="AE184">
-        <v>25838.3905</v>
-      </c>
-    </row>
-    <row r="185">
+        <v>25838.390500000001</v>
+      </c>
+    </row>
+    <row r="185" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>409</v>
       </c>
@@ -11365,7 +11661,7 @@
         <v>59</v>
       </c>
       <c r="AB185">
-        <v>46.8363</v>
+        <v>46.836300000000001</v>
       </c>
       <c r="AC185">
         <v>103.07092</v>
@@ -11374,10 +11670,10 @@
         <v>1564954</v>
       </c>
       <c r="AE185">
-        <v>1564953.688</v>
-      </c>
-    </row>
-    <row r="186">
+        <v>1564953.6880000001</v>
+      </c>
+    </row>
+    <row r="186" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>411</v>
       </c>
@@ -11406,7 +11702,7 @@
         <v>33</v>
       </c>
       <c r="AB186">
-        <v>-9.127230000000001</v>
+        <v>-9.1272300000000008</v>
       </c>
       <c r="AC186">
         <v>124.27427</v>
@@ -11415,10 +11711,10 @@
         <v>2578</v>
       </c>
       <c r="AE186">
-        <v>2578.265425</v>
-      </c>
-    </row>
-    <row r="187">
+        <v>2578.2654250000001</v>
+      </c>
+    </row>
+    <row r="187" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>412</v>
       </c>
@@ -11459,10 +11755,10 @@
         <v>273981</v>
       </c>
       <c r="AE187">
-        <v>273981.2237</v>
-      </c>
-    </row>
-    <row r="188">
+        <v>273981.22369999997</v>
+      </c>
+    </row>
+    <row r="188" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>186</v>
       </c>
@@ -11497,19 +11793,19 @@
         <v>33</v>
       </c>
       <c r="AB188">
-        <v>41.09913</v>
+        <v>41.099130000000002</v>
       </c>
       <c r="AC188">
-        <v>-3.84711</v>
+        <v>-3.8471099999999998</v>
       </c>
       <c r="AD188">
         <v>1060248</v>
       </c>
       <c r="AE188">
-        <v>1060247.985</v>
-      </c>
-    </row>
-    <row r="189">
+        <v>1060247.9850000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>414</v>
       </c>
@@ -11562,10 +11858,10 @@
         <v>39</v>
       </c>
       <c r="AB189">
-        <v>16.12316</v>
+        <v>16.123159999999999</v>
       </c>
       <c r="AC189">
-        <v>-88.2129</v>
+        <v>-88.212900000000005</v>
       </c>
       <c r="AD189">
         <v>1450</v>
@@ -11574,7 +11870,7 @@
         <v>1449.95064</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>417</v>
       </c>
@@ -11609,19 +11905,19 @@
         <v>33</v>
       </c>
       <c r="AB190">
-        <v>-7.81253</v>
+        <v>-7.8125299999999998</v>
       </c>
       <c r="AC190">
-        <v>74.29358999999999</v>
+        <v>74.293589999999995</v>
       </c>
       <c r="AD190">
         <v>753175</v>
       </c>
       <c r="AE190">
-        <v>753174.5746000002</v>
-      </c>
-    </row>
-    <row r="191">
+        <v>753174.57460000017</v>
+      </c>
+    </row>
+    <row r="191" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>419</v>
       </c>
@@ -11653,10 +11949,10 @@
         <v>59</v>
       </c>
       <c r="AB191">
-        <v>38.528</v>
+        <v>38.527999999999999</v>
       </c>
       <c r="AC191">
-        <v>71.03659</v>
+        <v>71.036590000000004</v>
       </c>
       <c r="AD191">
         <v>142401</v>
@@ -11665,7 +11961,7 @@
         <v>142400.8008</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>415</v>
       </c>
@@ -11700,19 +11996,19 @@
         <v>33</v>
       </c>
       <c r="AB192">
-        <v>17.22412</v>
+        <v>17.224119999999999</v>
       </c>
       <c r="AC192">
-        <v>-88.01936000000001</v>
+        <v>-88.019360000000006</v>
       </c>
       <c r="AD192">
         <v>54990</v>
       </c>
       <c r="AE192">
-        <v>54990.19842</v>
-      </c>
-    </row>
-    <row r="193">
+        <v>54990.198420000001</v>
+      </c>
+    </row>
+    <row r="193" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>421</v>
       </c>
@@ -11753,7 +12049,7 @@
         <v>435659.2121</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>137</v>
       </c>
@@ -11785,7 +12081,7 @@
         <v>33</v>
       </c>
       <c r="AB194">
-        <v>16.11342</v>
+        <v>16.113420000000001</v>
       </c>
       <c r="AC194">
         <v>30.22279</v>
@@ -11794,10 +12090,10 @@
         <v>1915609</v>
       </c>
       <c r="AE194">
-        <v>1915608.674</v>
-      </c>
-    </row>
-    <row r="195">
+        <v>1915608.6740000001</v>
+      </c>
+    </row>
+    <row r="195" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>422</v>
       </c>
@@ -11835,7 +12131,7 @@
         <v>42.79965</v>
       </c>
       <c r="AC195">
-        <v>26.18322</v>
+        <v>26.183219999999999</v>
       </c>
       <c r="AD195">
         <v>145698</v>
@@ -11844,7 +12140,7 @@
         <v>145697.603</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>424</v>
       </c>
@@ -11879,7 +12175,7 @@
         <v>33</v>
       </c>
       <c r="AB196">
-        <v>-3.81974</v>
+        <v>-3.8197399999999999</v>
       </c>
       <c r="AC196">
         <v>-154.72725</v>
@@ -11888,10 +12184,10 @@
         <v>1641797</v>
       </c>
       <c r="AE196">
-        <v>1641797.494</v>
-      </c>
-    </row>
-    <row r="197">
+        <v>1641797.4939999999</v>
+      </c>
+    </row>
+    <row r="197" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>425</v>
       </c>
@@ -11950,19 +12246,19 @@
         <v>56</v>
       </c>
       <c r="AB197">
-        <v>15.01851</v>
+        <v>15.018509999999999</v>
       </c>
       <c r="AC197">
-        <v>-72.50386</v>
+        <v>-72.503860000000003</v>
       </c>
       <c r="AD197">
         <v>13111</v>
       </c>
       <c r="AE197">
-        <v>13110.70344</v>
-      </c>
-    </row>
-    <row r="198">
+        <v>13110.703439999999</v>
+      </c>
+    </row>
+    <row r="198" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>426</v>
       </c>
@@ -11991,10 +12287,10 @@
         <v>33</v>
       </c>
       <c r="AB198">
-        <v>15.85001</v>
+        <v>15.850009999999999</v>
       </c>
       <c r="AC198">
-        <v>-78.63333</v>
+        <v>-78.633330000000001</v>
       </c>
       <c r="AD198">
         <v>1553</v>
@@ -12003,7 +12299,7 @@
         <v>1553.214326</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>271</v>
       </c>
@@ -12038,10 +12334,10 @@
         <v>33</v>
       </c>
       <c r="AB199">
-        <v>67.31804</v>
+        <v>67.318039999999996</v>
       </c>
       <c r="AC199">
-        <v>14.01682</v>
+        <v>14.016819999999999</v>
       </c>
       <c r="AD199">
         <v>1256755</v>
@@ -12050,7 +12346,7 @@
         <v>1256754.973</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>427</v>
       </c>
@@ -12088,7 +12384,7 @@
         <v>45.87679</v>
       </c>
       <c r="AC200">
-        <v>-56.38553</v>
+        <v>-56.385530000000003</v>
       </c>
       <c r="AD200">
         <v>12641</v>
@@ -12097,7 +12393,7 @@
         <v>12640.74524</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>429</v>
       </c>
@@ -12132,16 +12428,16 @@
         <v>-23.22336</v>
       </c>
       <c r="AC201">
-        <v>-58.40567</v>
+        <v>-58.405670000000001</v>
       </c>
       <c r="AD201">
         <v>400752</v>
       </c>
       <c r="AE201">
-        <v>400752.4479000001</v>
-      </c>
-    </row>
-    <row r="202">
+        <v>400752.44790000009</v>
+      </c>
+    </row>
+    <row r="202" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>431</v>
       </c>
@@ -12176,10 +12472,10 @@
         <v>33</v>
       </c>
       <c r="AB202">
-        <v>-21.77686</v>
+        <v>-21.776859999999999</v>
       </c>
       <c r="AC202">
-        <v>54.71973</v>
+        <v>54.719729999999998</v>
       </c>
       <c r="AD202">
         <v>317665</v>
@@ -12188,7 +12484,7 @@
         <v>317665.1825</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>266</v>
       </c>
@@ -12223,7 +12519,7 @@
         <v>33</v>
       </c>
       <c r="AB203">
-        <v>46.11552</v>
+        <v>46.115519999999997</v>
       </c>
       <c r="AC203">
         <v>14.81268</v>
@@ -12235,7 +12531,7 @@
         <v>20436.23849</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>433</v>
       </c>
@@ -12270,19 +12566,19 @@
         <v>33</v>
       </c>
       <c r="AB204">
-        <v>54.19319</v>
+        <v>54.193190000000001</v>
       </c>
       <c r="AC204">
-        <v>-4.56787</v>
+        <v>-4.5678700000000001</v>
       </c>
       <c r="AD204">
         <v>4541</v>
       </c>
       <c r="AE204">
-        <v>4540.893665</v>
-      </c>
-    </row>
-    <row r="205">
+        <v>4540.8936649999996</v>
+      </c>
+    </row>
+    <row r="205" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>435</v>
       </c>
@@ -12320,7 +12616,7 @@
         <v>20.1371</v>
       </c>
       <c r="AC205">
-        <v>78.41670999999999</v>
+        <v>78.416709999999995</v>
       </c>
       <c r="AD205">
         <v>4804679</v>
@@ -12329,7 +12625,7 @@
         <v>4804678.648</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>437</v>
       </c>
@@ -12367,7 +12663,7 @@
         <v>-21.02186</v>
       </c>
       <c r="AC206">
-        <v>163.24568</v>
+        <v>163.24567999999999</v>
       </c>
       <c r="AD206">
         <v>1198283</v>
@@ -12376,7 +12672,7 @@
         <v>1198282.794</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>439</v>
       </c>
@@ -12408,19 +12704,19 @@
         <v>59</v>
       </c>
       <c r="AB207">
-        <v>17.41524</v>
+        <v>17.415240000000001</v>
       </c>
       <c r="AC207">
-        <v>9.40085</v>
+        <v>9.4008500000000002</v>
       </c>
       <c r="AD207">
         <v>1181113</v>
       </c>
       <c r="AE207">
-        <v>1181112.974</v>
-      </c>
-    </row>
-    <row r="208">
+        <v>1181112.9739999999</v>
+      </c>
+    </row>
+    <row r="208" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>441</v>
       </c>
@@ -12455,19 +12751,19 @@
         <v>33</v>
       </c>
       <c r="AB208">
-        <v>19.54041</v>
+        <v>19.540410000000001</v>
       </c>
       <c r="AC208">
-        <v>57.7514</v>
+        <v>57.751399999999997</v>
       </c>
       <c r="AD208">
         <v>864661</v>
       </c>
       <c r="AE208">
-        <v>864660.6732</v>
-      </c>
-    </row>
-    <row r="209">
+        <v>864660.67319999996</v>
+      </c>
+    </row>
+    <row r="209" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>443</v>
       </c>
@@ -12517,16 +12813,16 @@
         <v>35.18506</v>
       </c>
       <c r="AC209">
-        <v>-4.305990000000002</v>
+        <v>-4.3059900000000022</v>
       </c>
       <c r="AD209">
         <v>4</v>
       </c>
       <c r="AE209">
-        <v>3.738562293</v>
-      </c>
-    </row>
-    <row r="210">
+        <v>3.7385622930000002</v>
+      </c>
+    </row>
+    <row r="210" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>444</v>
       </c>
@@ -12555,7 +12851,7 @@
         <v>33</v>
       </c>
       <c r="AB210">
-        <v>9.991239999999999</v>
+        <v>9.9912399999999995</v>
       </c>
       <c r="AC210">
         <v>92.19838</v>
@@ -12564,10 +12860,10 @@
         <v>671991</v>
       </c>
       <c r="AE210">
-        <v>671991.0163</v>
-      </c>
-    </row>
-    <row r="211">
+        <v>671991.01630000002</v>
+      </c>
+    </row>
+    <row r="211" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>274</v>
       </c>
@@ -12611,10 +12907,10 @@
         <v>2861551</v>
       </c>
       <c r="AE211">
-        <v>2861551.097</v>
-      </c>
-    </row>
-    <row r="212">
+        <v>2861551.0970000001</v>
+      </c>
+    </row>
+    <row r="212" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>317</v>
       </c>
@@ -12649,19 +12945,19 @@
         <v>33</v>
       </c>
       <c r="AB212">
-        <v>6.29025</v>
+        <v>6.2902500000000003</v>
       </c>
       <c r="AC212">
-        <v>-58.45109</v>
+        <v>-58.451090000000001</v>
       </c>
       <c r="AD212">
         <v>345516</v>
       </c>
       <c r="AE212">
-        <v>345516.279</v>
-      </c>
-    </row>
-    <row r="213">
+        <v>345516.27899999998</v>
+      </c>
+    </row>
+    <row r="213" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>445</v>
       </c>
@@ -12699,7 +12995,7 @@
         <v>2.46393</v>
       </c>
       <c r="AC213">
-        <v>73.0855</v>
+        <v>73.085499999999996</v>
       </c>
       <c r="AD213">
         <v>924131</v>
@@ -12708,7 +13004,7 @@
         <v>924130.53</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>447</v>
       </c>
@@ -12743,19 +13039,19 @@
         <v>33</v>
       </c>
       <c r="AB214">
-        <v>-34.15741</v>
+        <v>-34.157409999999999</v>
       </c>
       <c r="AC214">
-        <v>-54.78946</v>
+        <v>-54.789459999999998</v>
       </c>
       <c r="AD214">
         <v>320453</v>
       </c>
       <c r="AE214">
-        <v>320452.6077</v>
-      </c>
-    </row>
-    <row r="215">
+        <v>320452.60769999999</v>
+      </c>
+    </row>
+    <row r="215" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>449</v>
       </c>
@@ -12790,19 +13086,19 @@
         <v>33</v>
       </c>
       <c r="AB215">
-        <v>43.3518</v>
+        <v>43.351799999999997</v>
       </c>
       <c r="AC215">
-        <v>7.58608</v>
+        <v>7.5860799999999999</v>
       </c>
       <c r="AD215">
         <v>291</v>
       </c>
       <c r="AE215">
-        <v>290.5136861</v>
-      </c>
-    </row>
-    <row r="216">
+        <v>290.51368609999997</v>
+      </c>
+    </row>
+    <row r="216" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>451</v>
       </c>
@@ -12834,10 +13130,10 @@
         <v>59</v>
       </c>
       <c r="AB216">
-        <v>44.03168</v>
+        <v>44.031680000000001</v>
       </c>
       <c r="AC216">
-        <v>20.80693</v>
+        <v>20.806930000000001</v>
       </c>
       <c r="AD216">
         <v>88333</v>
@@ -12846,7 +13142,7 @@
         <v>88332.90221</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>453</v>
       </c>
@@ -12881,19 +13177,19 @@
         <v>33</v>
       </c>
       <c r="AB217">
-        <v>7.70602</v>
+        <v>7.7060199999999996</v>
       </c>
       <c r="AC217">
-        <v>1.15563</v>
+        <v>1.1556299999999999</v>
       </c>
       <c r="AD217">
         <v>72151</v>
       </c>
       <c r="AE217">
-        <v>72151.43150000001</v>
-      </c>
-    </row>
-    <row r="218">
+        <v>72151.431500000006</v>
+      </c>
+    </row>
+    <row r="218" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>455</v>
       </c>
@@ -12928,10 +13224,10 @@
         <v>33</v>
       </c>
       <c r="AB218">
-        <v>13.16453</v>
+        <v>13.164529999999999</v>
       </c>
       <c r="AC218">
-        <v>107.99693</v>
+        <v>107.99693000000001</v>
       </c>
       <c r="AD218">
         <v>1079094</v>
@@ -12940,7 +13236,7 @@
         <v>1079093.76</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>457</v>
       </c>
@@ -13002,16 +13298,16 @@
         <v>-56.51867</v>
       </c>
       <c r="AC219">
-        <v>-31.27742</v>
+        <v>-31.277419999999999</v>
       </c>
       <c r="AD219">
         <v>1241743</v>
       </c>
       <c r="AE219">
-        <v>1241743.427</v>
-      </c>
-    </row>
-    <row r="220">
+        <v>1241743.4269999999</v>
+      </c>
+    </row>
+    <row r="220" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>459</v>
       </c>
@@ -13046,7 +13342,7 @@
         <v>33</v>
       </c>
       <c r="AB220">
-        <v>31.24507</v>
+        <v>31.245069999999998</v>
       </c>
       <c r="AC220">
         <v>36.7866</v>
@@ -13055,10 +13351,10 @@
         <v>89444</v>
       </c>
       <c r="AE220">
-        <v>89443.77602</v>
-      </c>
-    </row>
-    <row r="221">
+        <v>89443.776020000005</v>
+      </c>
+    </row>
+    <row r="221" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>461</v>
       </c>
@@ -13105,19 +13401,19 @@
         <v>39</v>
       </c>
       <c r="AB221">
-        <v>35.87852</v>
+        <v>35.878520000000002</v>
       </c>
       <c r="AC221">
-        <v>-5.31943</v>
+        <v>-5.3194299999999997</v>
       </c>
       <c r="AD221">
         <v>53</v>
       </c>
       <c r="AE221">
-        <v>53.21027835</v>
-      </c>
-    </row>
-    <row r="222">
+        <v>53.210278350000003</v>
+      </c>
+    </row>
+    <row r="222" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>462</v>
       </c>
@@ -13152,16 +13448,16 @@
         <v>27.42117</v>
       </c>
       <c r="AC222">
-        <v>90.42016</v>
+        <v>90.420159999999996</v>
       </c>
       <c r="AD222">
         <v>40035</v>
       </c>
       <c r="AE222">
-        <v>40035.13991</v>
-      </c>
-    </row>
-    <row r="223">
+        <v>40035.139909999998</v>
+      </c>
+    </row>
+    <row r="223" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>464</v>
       </c>
@@ -13193,19 +13489,19 @@
         <v>59</v>
       </c>
       <c r="AB223">
-        <v>41.90318</v>
+        <v>41.903179999999999</v>
       </c>
       <c r="AC223">
-        <v>12.45328</v>
+        <v>12.453279999999999</v>
       </c>
       <c r="AD223">
         <v>1</v>
       </c>
       <c r="AE223">
-        <v>0.566205694</v>
-      </c>
-    </row>
-    <row r="224">
+        <v>0.56620569399999998</v>
+      </c>
+    </row>
+    <row r="224" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>466</v>
       </c>
@@ -13237,7 +13533,7 @@
         <v>59</v>
       </c>
       <c r="AB224">
-        <v>47.16502</v>
+        <v>47.165019999999998</v>
       </c>
       <c r="AC224">
         <v>19.41253</v>
@@ -13246,10 +13542,10 @@
         <v>93001</v>
       </c>
       <c r="AE224">
-        <v>93001.38933999999</v>
-      </c>
-    </row>
-    <row r="225">
+        <v>93001.389339999994</v>
+      </c>
+    </row>
+    <row r="225" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>468</v>
       </c>
@@ -13284,19 +13580,19 @@
         <v>33</v>
       </c>
       <c r="AB225">
-        <v>13.73398</v>
+        <v>13.733980000000001</v>
       </c>
       <c r="AC225">
-        <v>-69.67519</v>
+        <v>-69.675190000000001</v>
       </c>
       <c r="AD225">
         <v>30197</v>
       </c>
       <c r="AE225">
-        <v>30196.5565</v>
-      </c>
-    </row>
-    <row r="226">
+        <v>30196.556499999999</v>
+      </c>
+    </row>
+    <row r="226" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>470</v>
       </c>
@@ -13334,7 +13630,7 @@
         <v>-1.12276</v>
       </c>
       <c r="AC226">
-        <v>5.83364</v>
+        <v>5.8336399999999999</v>
       </c>
       <c r="AD226">
         <v>330928</v>
@@ -13343,7 +13639,7 @@
         <v>330928.1973</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>472</v>
       </c>
@@ -13402,19 +13698,19 @@
         <v>56</v>
       </c>
       <c r="AB227">
-        <v>72.92452</v>
+        <v>72.924520000000001</v>
       </c>
       <c r="AC227">
-        <v>37.46457</v>
+        <v>37.464570000000002</v>
       </c>
       <c r="AD227">
         <v>3397</v>
       </c>
       <c r="AE227">
-        <v>3397.133426</v>
-      </c>
-    </row>
-    <row r="228">
+        <v>3397.1334259999999</v>
+      </c>
+    </row>
+    <row r="228" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>473</v>
       </c>
@@ -13446,7 +13742,7 @@
         <v>14.38097</v>
       </c>
       <c r="AC228">
-        <v>-80.30177999999999</v>
+        <v>-80.301779999999994</v>
       </c>
       <c r="AD228">
         <v>2842</v>
@@ -13455,7 +13751,7 @@
         <v>2842.327632</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>474</v>
       </c>
@@ -13487,10 +13783,10 @@
         <v>59</v>
       </c>
       <c r="AB229">
-        <v>43.93869</v>
+        <v>43.938690000000001</v>
       </c>
       <c r="AC229">
-        <v>12.46291</v>
+        <v>12.462910000000001</v>
       </c>
       <c r="AD229">
         <v>58</v>
@@ -13499,7 +13795,7 @@
         <v>58.46616607</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>476</v>
       </c>
@@ -13585,7 +13881,7 @@
         <v>15.30381</v>
       </c>
       <c r="AC230">
-        <v>-69.65326</v>
+        <v>-69.653260000000003</v>
       </c>
       <c r="AD230">
         <v>1113</v>
@@ -13594,7 +13890,7 @@
         <v>1113.317276</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>477</v>
       </c>
@@ -13629,7 +13925,7 @@
         <v>33</v>
       </c>
       <c r="AB231">
-        <v>5.80194</v>
+        <v>5.8019400000000001</v>
       </c>
       <c r="AC231">
         <v>-55.35857</v>
@@ -13641,7 +13937,7 @@
         <v>278588.9878</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>226</v>
       </c>
@@ -13676,19 +13972,19 @@
         <v>33</v>
       </c>
       <c r="AB232">
-        <v>64.73246</v>
+        <v>64.732460000000003</v>
       </c>
       <c r="AC232">
-        <v>-18.46504</v>
+        <v>-18.465039999999998</v>
       </c>
       <c r="AD232">
         <v>865631</v>
       </c>
       <c r="AE232">
-        <v>865630.9691</v>
-      </c>
-    </row>
-    <row r="233">
+        <v>865630.96909999999</v>
+      </c>
+    </row>
+    <row r="233" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>479</v>
       </c>
@@ -13741,19 +14037,19 @@
         <v>39</v>
       </c>
       <c r="AB233">
-        <v>32.81282</v>
+        <v>32.812820000000002</v>
       </c>
       <c r="AC233">
-        <v>25.70163</v>
+        <v>25.701630000000002</v>
       </c>
       <c r="AD233">
         <v>8114</v>
       </c>
       <c r="AE233">
-        <v>8113.729769</v>
-      </c>
-    </row>
-    <row r="234">
+        <v>8113.7297689999996</v>
+      </c>
+    </row>
+    <row r="234" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>480</v>
       </c>
@@ -13788,7 +14084,7 @@
         <v>33</v>
       </c>
       <c r="AB234">
-        <v>-3.05164</v>
+        <v>-3.0516399999999999</v>
       </c>
       <c r="AC234">
         <v>117.74829</v>
@@ -13797,10 +14093,10 @@
         <v>7906619</v>
       </c>
       <c r="AE234">
-        <v>7906619.381</v>
-      </c>
-    </row>
-    <row r="235">
+        <v>7906619.3810000001</v>
+      </c>
+    </row>
+    <row r="235" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>482</v>
       </c>
@@ -13859,10 +14155,10 @@
         <v>39</v>
       </c>
       <c r="AB235">
-        <v>-51.66866</v>
+        <v>-51.668660000000003</v>
       </c>
       <c r="AC235">
-        <v>-58.346</v>
+        <v>-58.345999999999997</v>
       </c>
       <c r="AD235">
         <v>562938</v>
@@ -13871,7 +14167,7 @@
         <v>562938.29</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>485</v>
       </c>
@@ -13930,19 +14226,19 @@
         <v>56</v>
       </c>
       <c r="AB236">
-        <v>-36.25493</v>
+        <v>-36.254930000000002</v>
       </c>
       <c r="AC236">
-        <v>-55.16096</v>
+        <v>-55.160960000000003</v>
       </c>
       <c r="AD236">
         <v>41414</v>
       </c>
       <c r="AE236">
-        <v>41413.8092</v>
-      </c>
-    </row>
-    <row r="237">
+        <v>41413.809200000003</v>
+      </c>
+    </row>
+    <row r="237" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>486</v>
       </c>
@@ -13971,19 +14267,19 @@
         <v>33</v>
       </c>
       <c r="AB237">
-        <v>60.70916</v>
+        <v>60.709159999999997</v>
       </c>
       <c r="AC237">
-        <v>-130.4678</v>
+        <v>-130.46780000000001</v>
       </c>
       <c r="AD237">
         <v>5193058</v>
       </c>
       <c r="AE237">
-        <v>5193058.289</v>
-      </c>
-    </row>
-    <row r="238">
+        <v>5193058.2889999999</v>
+      </c>
+    </row>
+    <row r="238" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>487</v>
       </c>
@@ -14015,7 +14311,7 @@
         <v>59</v>
       </c>
       <c r="AB238">
-        <v>42.54516</v>
+        <v>42.545160000000003</v>
       </c>
       <c r="AC238">
         <v>1.57585</v>
@@ -14024,10 +14320,10 @@
         <v>468</v>
       </c>
       <c r="AE238">
-        <v>467.9036281</v>
-      </c>
-    </row>
-    <row r="239">
+        <v>467.90362809999999</v>
+      </c>
+    </row>
+    <row r="239" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>489</v>
       </c>
@@ -14062,10 +14358,10 @@
         <v>33</v>
       </c>
       <c r="AB239">
-        <v>18.03685</v>
+        <v>18.036850000000001</v>
       </c>
       <c r="AC239">
-        <v>-63.19595</v>
+        <v>-63.195950000000003</v>
       </c>
       <c r="AD239">
         <v>1155</v>
@@ -14074,7 +14370,7 @@
         <v>1155.029918</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>491</v>
       </c>
@@ -14109,10 +14405,10 @@
         <v>33</v>
       </c>
       <c r="AB240">
-        <v>28.69612</v>
+        <v>28.696120000000001</v>
       </c>
       <c r="AC240">
-        <v>2.70792</v>
+        <v>2.7079200000000001</v>
       </c>
       <c r="AD240">
         <v>2444284</v>
@@ -14121,7 +14417,7 @@
         <v>2444283.56</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>493</v>
       </c>
@@ -14156,19 +14452,19 @@
         <v>33</v>
       </c>
       <c r="AB241">
-        <v>6.13045</v>
+        <v>6.1304499999999997</v>
       </c>
       <c r="AC241">
-        <v>-5.52125</v>
+        <v>-5.5212500000000002</v>
       </c>
       <c r="AD241">
         <v>492520</v>
       </c>
       <c r="AE241">
-        <v>492520.1653</v>
-      </c>
-    </row>
-    <row r="242">
+        <v>492520.16529999999</v>
+      </c>
+    </row>
+    <row r="242" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>495</v>
       </c>
@@ -14203,10 +14499,10 @@
         <v>33</v>
       </c>
       <c r="AB242">
-        <v>-18.57568</v>
+        <v>-18.575679999999998</v>
       </c>
       <c r="AC242">
-        <v>36.57083</v>
+        <v>36.570830000000001</v>
       </c>
       <c r="AD242">
         <v>1352537</v>
@@ -14215,7 +14511,7 @@
         <v>1352536.737</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>497</v>
       </c>
@@ -14262,19 +14558,19 @@
         <v>39</v>
       </c>
       <c r="AB243">
-        <v>35.91444</v>
+        <v>35.914439999999999</v>
       </c>
       <c r="AC243">
-        <v>-5.41983</v>
+        <v>-5.4198300000000001</v>
       </c>
       <c r="AD243">
         <v>1</v>
       </c>
       <c r="AE243">
-        <v>0.785737099</v>
-      </c>
-    </row>
-    <row r="244">
+        <v>0.78573709899999999</v>
+      </c>
+    </row>
+    <row r="244" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>498</v>
       </c>
@@ -14306,7 +14602,7 @@
         <v>59</v>
       </c>
       <c r="AB244">
-        <v>49.73926</v>
+        <v>49.739260000000002</v>
       </c>
       <c r="AC244">
         <v>15.33131</v>
@@ -14315,10 +14611,10 @@
         <v>78842</v>
       </c>
       <c r="AE244">
-        <v>78841.84408</v>
-      </c>
-    </row>
-    <row r="245">
+        <v>78841.844079999995</v>
+      </c>
+    </row>
+    <row r="245" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>500</v>
       </c>
@@ -14353,7 +14649,7 @@
         <v>33</v>
       </c>
       <c r="AB245">
-        <v>-1.67162</v>
+        <v>-1.6716200000000001</v>
       </c>
       <c r="AC245">
         <v>10.46771</v>
@@ -14365,7 +14661,7 @@
         <v>463413.3578</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>220</v>
       </c>
@@ -14409,10 +14705,10 @@
         <v>14559566</v>
       </c>
       <c r="AE246">
-        <v>14559566.31</v>
-      </c>
-    </row>
-    <row r="247">
+        <v>14559566.310000001</v>
+      </c>
+    </row>
+    <row r="247" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>502</v>
       </c>
@@ -14432,10 +14728,10 @@
         <v>12524451</v>
       </c>
       <c r="AE247">
-        <v>12524451.06</v>
-      </c>
-    </row>
-    <row r="248">
+        <v>12524451.060000001</v>
+      </c>
+    </row>
+    <row r="248" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>503</v>
       </c>
@@ -14464,19 +14760,19 @@
         <v>33</v>
       </c>
       <c r="AB248">
-        <v>15.79723</v>
+        <v>15.797230000000001</v>
       </c>
       <c r="AC248">
-        <v>-79.85556</v>
+        <v>-79.855559999999997</v>
       </c>
       <c r="AD248">
         <v>1553</v>
       </c>
       <c r="AE248">
-        <v>1553.311591</v>
-      </c>
-    </row>
-    <row r="249">
+        <v>1553.3115909999999</v>
+      </c>
+    </row>
+    <row r="249" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>504</v>
       </c>
@@ -14511,19 +14807,19 @@
         <v>33</v>
       </c>
       <c r="AB249">
-        <v>-17.30644</v>
+        <v>-17.306439999999998</v>
       </c>
       <c r="AC249">
-        <v>42.09477</v>
+        <v>42.094769999999997</v>
       </c>
       <c r="AD249">
         <v>62824</v>
       </c>
       <c r="AE249">
-        <v>62824.02726</v>
-      </c>
-    </row>
-    <row r="250">
+        <v>62824.027260000003</v>
+      </c>
+    </row>
+    <row r="250" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>505</v>
       </c>
@@ -14558,19 +14854,19 @@
         <v>33</v>
       </c>
       <c r="AB250">
-        <v>71.11408</v>
+        <v>71.114080000000001</v>
       </c>
       <c r="AC250">
-        <v>-5.25539</v>
+        <v>-5.2553900000000002</v>
       </c>
       <c r="AD250">
         <v>293291</v>
       </c>
       <c r="AE250">
-        <v>293290.5763</v>
-      </c>
-    </row>
-    <row r="251">
+        <v>293290.57630000002</v>
+      </c>
+    </row>
+    <row r="251" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>507</v>
       </c>
@@ -14605,19 +14901,19 @@
         <v>33</v>
       </c>
       <c r="AB251">
-        <v>14.293</v>
+        <v>14.292999999999999</v>
       </c>
       <c r="AC251">
-        <v>49.98167</v>
+        <v>49.981670000000001</v>
       </c>
       <c r="AD251">
         <v>980397</v>
       </c>
       <c r="AE251">
-        <v>980397.204</v>
-      </c>
-    </row>
-    <row r="252">
+        <v>980397.20400000003</v>
+      </c>
+    </row>
+    <row r="252" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>509</v>
       </c>
@@ -14664,7 +14960,7 @@
         <v>39</v>
       </c>
       <c r="AB252">
-        <v>37.24233</v>
+        <v>37.242330000000003</v>
       </c>
       <c r="AC252">
         <v>131.86633</v>
@@ -14673,10 +14969,10 @@
         <v>1624</v>
       </c>
       <c r="AE252">
-        <v>1623.62846</v>
-      </c>
-    </row>
-    <row r="253">
+        <v>1623.6284599999999</v>
+      </c>
+    </row>
+    <row r="253" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>75</v>
       </c>
@@ -14711,19 +15007,19 @@
         <v>33</v>
       </c>
       <c r="AB253">
-        <v>38.45681</v>
+        <v>38.456809999999997</v>
       </c>
       <c r="AC253">
-        <v>-98.38799</v>
+        <v>-98.387990000000002</v>
       </c>
       <c r="AD253">
         <v>10392443</v>
       </c>
       <c r="AE253">
-        <v>10392443.11</v>
-      </c>
-    </row>
-    <row r="254">
+        <v>10392443.109999999</v>
+      </c>
+    </row>
+    <row r="254" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>123</v>
       </c>
@@ -14758,7 +15054,7 @@
         <v>33</v>
       </c>
       <c r="AB254">
-        <v>40.8141</v>
+        <v>40.814100000000003</v>
       </c>
       <c r="AC254">
         <v>12.61505</v>
@@ -14767,10 +15063,10 @@
         <v>837225</v>
       </c>
       <c r="AE254">
-        <v>837224.5569</v>
-      </c>
-    </row>
-    <row r="255">
+        <v>837224.55689999997</v>
+      </c>
+    </row>
+    <row r="255" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>511</v>
       </c>
@@ -14805,19 +15101,19 @@
         <v>33</v>
       </c>
       <c r="AB255">
-        <v>32.36898</v>
+        <v>32.368980000000001</v>
       </c>
       <c r="AC255">
-        <v>-64.80692000000001</v>
+        <v>-64.806920000000005</v>
       </c>
       <c r="AD255">
         <v>464453</v>
       </c>
       <c r="AE255">
-        <v>464453.075</v>
-      </c>
-    </row>
-    <row r="256">
+        <v>464453.07500000001</v>
+      </c>
+    </row>
+    <row r="256" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>513</v>
       </c>
@@ -14873,10 +15169,10 @@
         <v>246</v>
       </c>
       <c r="AE256">
-        <v>245.903579</v>
-      </c>
-    </row>
-    <row r="257">
+        <v>245.90357900000001</v>
+      </c>
+    </row>
+    <row r="257" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>516</v>
       </c>
@@ -14932,7 +15228,7 @@
         <v>3.22641</v>
       </c>
       <c r="AC257">
-        <v>-88.84132</v>
+        <v>-88.841319999999996</v>
       </c>
       <c r="AD257">
         <v>17337</v>
@@ -14941,7 +15237,7 @@
         <v>17337.24221</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>517</v>
       </c>
@@ -14976,19 +15272,19 @@
         <v>33</v>
       </c>
       <c r="AB258">
-        <v>28.70724</v>
+        <v>28.707239999999999</v>
       </c>
       <c r="AC258">
-        <v>68.46558</v>
+        <v>68.465580000000003</v>
       </c>
       <c r="AD258">
         <v>1096404</v>
       </c>
       <c r="AE258">
-        <v>1096403.603</v>
-      </c>
-    </row>
-    <row r="259">
+        <v>1096403.6029999999</v>
+      </c>
+    </row>
+    <row r="259" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>519</v>
       </c>
@@ -15038,16 +15334,16 @@
         <v>35.17013</v>
       </c>
       <c r="AC259">
-        <v>-2.45308</v>
+        <v>-2.4530799999999999</v>
       </c>
       <c r="AD259">
         <v>26</v>
       </c>
       <c r="AE259">
-        <v>26.11627785</v>
-      </c>
-    </row>
-    <row r="260">
+        <v>26.116277849999999</v>
+      </c>
+    </row>
+    <row r="260" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>139</v>
       </c>
@@ -15082,19 +15378,19 @@
         <v>33</v>
       </c>
       <c r="AB260">
-        <v>27.35752</v>
+        <v>27.357520000000001</v>
       </c>
       <c r="AC260">
-        <v>30.06336</v>
+        <v>30.063359999999999</v>
       </c>
       <c r="AD260">
         <v>1226673</v>
       </c>
       <c r="AE260">
-        <v>1226673.099</v>
-      </c>
-    </row>
-    <row r="261">
+        <v>1226673.0989999999</v>
+      </c>
+    </row>
+    <row r="261" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>292</v>
       </c>
@@ -15129,19 +15425,19 @@
         <v>33</v>
       </c>
       <c r="AB261">
-        <v>-16.81658</v>
+        <v>-16.816579999999998</v>
       </c>
       <c r="AC261">
-        <v>60.11338</v>
+        <v>60.113379999999999</v>
       </c>
       <c r="AD261">
         <v>1280969</v>
       </c>
       <c r="AE261">
-        <v>1280968.84</v>
-      </c>
-    </row>
-    <row r="262">
+        <v>1280968.8400000001</v>
+      </c>
+    </row>
+    <row r="262" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>520</v>
       </c>
@@ -15176,19 +15472,19 @@
         <v>33</v>
       </c>
       <c r="AB262">
-        <v>41.07594</v>
+        <v>41.075940000000003</v>
       </c>
       <c r="AC262">
-        <v>19.78273</v>
+        <v>19.782730000000001</v>
       </c>
       <c r="AD262">
         <v>40954</v>
       </c>
       <c r="AE262">
-        <v>40953.54483</v>
-      </c>
-    </row>
-    <row r="263">
+        <v>40953.544829999999</v>
+      </c>
+    </row>
+    <row r="263" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>522</v>
       </c>
@@ -15247,19 +15543,19 @@
         <v>39</v>
       </c>
       <c r="AB263">
-        <v>23.98576</v>
+        <v>23.985759999999999</v>
       </c>
       <c r="AC263">
-        <v>-15.46474</v>
+        <v>-15.464740000000001</v>
       </c>
       <c r="AD263">
         <v>553988</v>
       </c>
       <c r="AE263">
-        <v>553988.0766</v>
-      </c>
-    </row>
-    <row r="264">
+        <v>553988.07660000003</v>
+      </c>
+    </row>
+    <row r="264" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>280</v>
       </c>
@@ -15294,24 +15590,24 @@
         <v>33</v>
       </c>
       <c r="AB264">
-        <v>53.14082</v>
+        <v>53.140819999999998</v>
       </c>
       <c r="AC264">
-        <v>4.68178</v>
+        <v>4.6817799999999998</v>
       </c>
       <c r="AD264">
         <v>99460</v>
       </c>
       <c r="AE264">
-        <v>99460.48933</v>
-      </c>
-    </row>
-    <row r="265">
+        <v>99460.489329999997</v>
+      </c>
+    </row>
+    <row r="265" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>524</v>
       </c>
       <c r="C265" t="s">
-        <v>431</v>
+        <v>524</v>
       </c>
       <c r="D265">
         <v>2239</v>
@@ -15338,7 +15634,7 @@
         <v>59</v>
       </c>
       <c r="AB265">
-        <v>-1.9991</v>
+        <v>-1.9991000000000001</v>
       </c>
       <c r="AC265">
         <v>29.92567</v>
@@ -15347,10 +15643,10 @@
         <v>25315</v>
       </c>
       <c r="AE265">
-        <v>25315.45209</v>
-      </c>
-    </row>
-    <row r="266">
+        <v>25315.452089999999</v>
+      </c>
+    </row>
+    <row r="266" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>526</v>
       </c>
@@ -15385,19 +15681,19 @@
         <v>33</v>
       </c>
       <c r="AB266">
-        <v>4.63158</v>
+        <v>4.6315799999999996</v>
       </c>
       <c r="AC266">
-        <v>109.45041</v>
+        <v>109.45041000000001</v>
       </c>
       <c r="AD266">
         <v>847078</v>
       </c>
       <c r="AE266">
-        <v>847078.3438</v>
-      </c>
-    </row>
-    <row r="267">
+        <v>847078.34380000003</v>
+      </c>
+    </row>
+    <row r="267" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>528</v>
       </c>
@@ -15459,16 +15755,16 @@
         <v>1.46058</v>
       </c>
       <c r="AC267">
-        <v>-81.43711999999999</v>
+        <v>-81.437119999999993</v>
       </c>
       <c r="AD267">
         <v>18663</v>
       </c>
       <c r="AE267">
-        <v>18663.01955</v>
-      </c>
-    </row>
-    <row r="268">
+        <v>18663.019550000001</v>
+      </c>
+    </row>
+    <row r="268" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>359</v>
       </c>
@@ -15503,19 +15799,19 @@
         <v>33</v>
       </c>
       <c r="AB268">
-        <v>19.10902</v>
+        <v>19.109020000000001</v>
       </c>
       <c r="AC268">
-        <v>-69.77134</v>
+        <v>-69.771339999999995</v>
       </c>
       <c r="AD268">
         <v>398852</v>
       </c>
       <c r="AE268">
-        <v>398851.9321</v>
-      </c>
-    </row>
-    <row r="269">
+        <v>398851.93209999998</v>
+      </c>
+    </row>
+    <row r="269" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>529</v>
       </c>
@@ -15550,7 +15846,7 @@
         <v>33</v>
       </c>
       <c r="AB269">
-        <v>7.23494</v>
+        <v>7.2349399999999999</v>
       </c>
       <c r="AC269">
         <v>-13.41098</v>
@@ -15562,7 +15858,7 @@
         <v>232907.7396</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>514</v>
       </c>
@@ -15597,10 +15893,10 @@
         <v>33</v>
       </c>
       <c r="AB270">
-        <v>11.80055</v>
+        <v>11.800549999999999</v>
       </c>
       <c r="AC270">
-        <v>42.7932</v>
+        <v>42.793199999999999</v>
       </c>
       <c r="AD270">
         <v>28895</v>
@@ -15609,7 +15905,7 @@
         <v>28895.09636</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>531</v>
       </c>
@@ -15668,7 +15964,7 @@
         <v>56</v>
       </c>
       <c r="AB271">
-        <v>69.29167</v>
+        <v>69.291669999999996</v>
       </c>
       <c r="AC271">
         <v>-8.5</v>
@@ -15680,7 +15976,7 @@
         <v>45531.91287</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>532</v>
       </c>
@@ -15715,7 +16011,7 @@
         <v>33</v>
       </c>
       <c r="AB272">
-        <v>34.86126</v>
+        <v>34.861260000000001</v>
       </c>
       <c r="AC272">
         <v>10.16292</v>
@@ -15724,10 +16020,10 @@
         <v>254796</v>
       </c>
       <c r="AE272">
-        <v>254795.9371</v>
-      </c>
-    </row>
-    <row r="273">
+        <v>254795.93710000001</v>
+      </c>
+    </row>
+    <row r="273" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>534</v>
       </c>
@@ -15762,19 +16058,19 @@
         <v>33</v>
       </c>
       <c r="AB273">
-        <v>-2.89652</v>
+        <v>-2.8965200000000002</v>
       </c>
       <c r="AC273">
-        <v>23.5802</v>
+        <v>23.580200000000001</v>
       </c>
       <c r="AD273">
         <v>2342345</v>
       </c>
       <c r="AE273">
-        <v>2342345.487</v>
-      </c>
-    </row>
-    <row r="274">
+        <v>2342345.4870000002</v>
+      </c>
+    </row>
+    <row r="274" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>536</v>
       </c>
@@ -15818,10 +16114,10 @@
         <v>2260601</v>
       </c>
       <c r="AE274">
-        <v>2260600.759</v>
-      </c>
-    </row>
-    <row r="275">
+        <v>2260600.7590000001</v>
+      </c>
+    </row>
+    <row r="275" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>538</v>
       </c>
@@ -15856,10 +16152,10 @@
         <v>33</v>
       </c>
       <c r="AB275">
-        <v>18.72715</v>
+        <v>18.727150000000002</v>
       </c>
       <c r="AC275">
-        <v>-60.57538</v>
+        <v>-60.575380000000003</v>
       </c>
       <c r="AD275">
         <v>112004</v>
@@ -15868,7 +16164,7 @@
         <v>112003.5377</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>540</v>
       </c>
@@ -15903,10 +16199,10 @@
         <v>33</v>
       </c>
       <c r="AB276">
-        <v>12.24262</v>
+        <v>12.242620000000001</v>
       </c>
       <c r="AC276">
-        <v>-62.05328</v>
+        <v>-62.053280000000001</v>
       </c>
       <c r="AD276">
         <v>25929</v>
@@ -15915,7 +16211,7 @@
         <v>25929.44268</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>542</v>
       </c>
@@ -15950,7 +16246,7 @@
         <v>33</v>
       </c>
       <c r="AB277">
-        <v>-29.09313</v>
+        <v>-29.093129999999999</v>
       </c>
       <c r="AC277">
         <v>167.92899</v>
@@ -15959,10 +16255,10 @@
         <v>430640</v>
       </c>
       <c r="AE277">
-        <v>430640.4739</v>
-      </c>
-    </row>
-    <row r="278">
+        <v>430640.47389999998</v>
+      </c>
+    </row>
+    <row r="278" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>544</v>
       </c>
@@ -15997,16 +16293,16 @@
         <v>46.80048</v>
       </c>
       <c r="AC278">
-        <v>8.229939999999999</v>
+        <v>8.2299399999999991</v>
       </c>
       <c r="AD278">
         <v>41270</v>
       </c>
       <c r="AE278">
-        <v>41270.47734</v>
-      </c>
-    </row>
-    <row r="279">
+        <v>41270.477339999998</v>
+      </c>
+    </row>
+    <row r="279" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>546</v>
       </c>
@@ -16041,10 +16337,10 @@
         <v>33</v>
       </c>
       <c r="AB279">
-        <v>10.15054</v>
+        <v>10.150539999999999</v>
       </c>
       <c r="AC279">
-        <v>167.48625</v>
+        <v>167.48625000000001</v>
       </c>
       <c r="AD279">
         <v>2004959</v>
@@ -16053,7 +16349,7 @@
         <v>2004958.808</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>548</v>
       </c>
@@ -16082,19 +16378,19 @@
         <v>33</v>
       </c>
       <c r="AB280">
-        <v>-26.82407</v>
+        <v>-26.824069999999999</v>
       </c>
       <c r="AC280">
-        <v>-107.43913</v>
+        <v>-107.43913000000001</v>
       </c>
       <c r="AD280">
         <v>729932</v>
       </c>
       <c r="AE280">
-        <v>729932.3374</v>
-      </c>
-    </row>
-    <row r="281">
+        <v>729932.33739999996</v>
+      </c>
+    </row>
+    <row r="281" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>549</v>
       </c>
@@ -16129,7 +16425,7 @@
         <v>33</v>
       </c>
       <c r="AB281">
-        <v>-24.60621</v>
+        <v>-24.606210000000001</v>
       </c>
       <c r="AC281">
         <v>-127.42138</v>
@@ -16138,10 +16434,10 @@
         <v>842344</v>
       </c>
       <c r="AE281">
-        <v>842344.1991</v>
-      </c>
-    </row>
-    <row r="282">
+        <v>842344.19909999997</v>
+      </c>
+    </row>
+    <row r="282" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>551</v>
       </c>
@@ -16173,7 +16469,7 @@
         <v>59</v>
       </c>
       <c r="AB282">
-        <v>47.20278</v>
+        <v>47.202779999999997</v>
       </c>
       <c r="AC282">
         <v>28.4648</v>
@@ -16182,10 +16478,10 @@
         <v>33856</v>
       </c>
       <c r="AE282">
-        <v>33855.6426</v>
-      </c>
-    </row>
-    <row r="283">
+        <v>33855.642599999999</v>
+      </c>
+    </row>
+    <row r="283" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>553</v>
       </c>
@@ -16217,16 +16513,16 @@
         <v>-54.87623</v>
       </c>
       <c r="AC283">
-        <v>158.65297</v>
+        <v>158.65297000000001</v>
       </c>
       <c r="AD283">
         <v>476413</v>
       </c>
       <c r="AE283">
-        <v>476412.8641</v>
-      </c>
-    </row>
-    <row r="284">
+        <v>476412.86410000001</v>
+      </c>
+    </row>
+    <row r="284" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>554</v>
       </c>
@@ -16264,7 +16560,7 @@
         <v>14.96773</v>
       </c>
       <c r="AC284">
-        <v>-60.21926</v>
+        <v>-60.219259999999998</v>
       </c>
       <c r="AD284">
         <v>48905</v>
@@ -16273,7 +16569,7 @@
         <v>48905.09809</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>240</v>
       </c>
@@ -16311,16 +16607,16 @@
         <v>14.0656</v>
       </c>
       <c r="AC285">
-        <v>-16.26891</v>
+        <v>-16.268910000000002</v>
       </c>
       <c r="AD285">
         <v>353555</v>
       </c>
       <c r="AE285">
-        <v>353554.9855</v>
-      </c>
-    </row>
-    <row r="286">
+        <v>353554.98550000001</v>
+      </c>
+    </row>
+    <row r="286" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>556</v>
       </c>
@@ -16358,16 +16654,16 @@
         <v>16.41743</v>
       </c>
       <c r="AC286">
-        <v>-62.47978</v>
+        <v>-62.479779999999998</v>
       </c>
       <c r="AD286">
         <v>7289</v>
       </c>
       <c r="AE286">
-        <v>7288.804817</v>
-      </c>
-    </row>
-    <row r="287">
+        <v>7288.8048170000002</v>
+      </c>
+    </row>
+    <row r="287" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>558</v>
       </c>
@@ -16402,19 +16698,19 @@
         <v>33</v>
       </c>
       <c r="AB287">
-        <v>13.15852</v>
+        <v>13.158519999999999</v>
       </c>
       <c r="AC287">
-        <v>-61.68907</v>
+        <v>-61.689070000000001</v>
       </c>
       <c r="AD287">
         <v>36641</v>
       </c>
       <c r="AE287">
-        <v>36640.77601</v>
-      </c>
-    </row>
-    <row r="288">
+        <v>36640.776010000001</v>
+      </c>
+    </row>
+    <row r="288" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>560</v>
       </c>
@@ -16449,19 +16745,19 @@
         <v>33</v>
       </c>
       <c r="AB288">
-        <v>75.13542</v>
+        <v>75.135419999999996</v>
       </c>
       <c r="AC288">
-        <v>-36.40807</v>
+        <v>-36.408070000000002</v>
       </c>
       <c r="AD288">
         <v>4437543</v>
       </c>
       <c r="AE288">
-        <v>4437543.214</v>
-      </c>
-    </row>
-    <row r="289">
+        <v>4437543.2139999997</v>
+      </c>
+    </row>
+    <row r="289" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>562</v>
       </c>
@@ -16496,19 +16792,19 @@
         <v>33</v>
       </c>
       <c r="AB289">
-        <v>-38.29427</v>
+        <v>-38.294269999999997</v>
       </c>
       <c r="AC289">
-        <v>77.54181</v>
+        <v>77.541809999999998</v>
       </c>
       <c r="AD289">
         <v>512252</v>
       </c>
       <c r="AE289">
-        <v>512251.8623</v>
-      </c>
-    </row>
-    <row r="290">
+        <v>512251.86229999998</v>
+      </c>
+    </row>
+    <row r="290" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>563</v>
       </c>
@@ -16543,19 +16839,19 @@
         <v>33</v>
       </c>
       <c r="AB290">
-        <v>-46.30785</v>
+        <v>-46.307850000000002</v>
       </c>
       <c r="AC290">
-        <v>51.21234</v>
+        <v>51.212339999999998</v>
       </c>
       <c r="AD290">
         <v>575822</v>
       </c>
       <c r="AE290">
-        <v>575821.6657</v>
-      </c>
-    </row>
-    <row r="291">
+        <v>575821.66570000001</v>
+      </c>
+    </row>
+    <row r="291" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>564</v>
       </c>
@@ -16590,19 +16886,19 @@
         <v>33</v>
       </c>
       <c r="AB291">
-        <v>21.60608</v>
+        <v>21.606079999999999</v>
       </c>
       <c r="AC291">
-        <v>-80.93245</v>
+        <v>-80.932450000000003</v>
       </c>
       <c r="AD291">
         <v>462964</v>
       </c>
       <c r="AE291">
-        <v>462964.0389</v>
-      </c>
-    </row>
-    <row r="292">
+        <v>462964.03889999999</v>
+      </c>
+    </row>
+    <row r="292" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>566</v>
       </c>
@@ -16649,7 +16945,7 @@
         <v>39</v>
       </c>
       <c r="AB292">
-        <v>43.90538</v>
+        <v>43.905380000000001</v>
       </c>
       <c r="AC292">
         <v>147.9443</v>
@@ -16658,10 +16954,10 @@
         <v>218735</v>
       </c>
       <c r="AE292">
-        <v>218735.0936</v>
-      </c>
-    </row>
-    <row r="293">
+        <v>218735.09359999999</v>
+      </c>
+    </row>
+    <row r="293" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>35</v>
       </c>
@@ -16696,7 +16992,7 @@
         <v>33</v>
       </c>
       <c r="AB293">
-        <v>24.34993</v>
+        <v>24.349930000000001</v>
       </c>
       <c r="AC293">
         <v>54.14593</v>
@@ -16705,10 +17001,10 @@
         <v>122932</v>
       </c>
       <c r="AE293">
-        <v>122931.7161</v>
-      </c>
-    </row>
-    <row r="294">
+        <v>122931.71610000001</v>
+      </c>
+    </row>
+    <row r="294" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>567</v>
       </c>
@@ -16764,16 +17060,16 @@
         <v>1.40778</v>
       </c>
       <c r="AC294">
-        <v>104.45239</v>
+        <v>104.45238999999999</v>
       </c>
       <c r="AD294">
         <v>287</v>
       </c>
       <c r="AE294">
-        <v>286.6073886</v>
-      </c>
-    </row>
-    <row r="295">
+        <v>286.60738859999998</v>
+      </c>
+    </row>
+    <row r="295" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>568</v>
       </c>
@@ -16808,16 +17104,16 @@
         <v>-13.45692</v>
       </c>
       <c r="AC295">
-        <v>27.79435</v>
+        <v>27.794350000000001</v>
       </c>
       <c r="AD295">
         <v>751192</v>
       </c>
       <c r="AE295">
-        <v>751191.6791</v>
-      </c>
-    </row>
-    <row r="296">
+        <v>751191.67909999995</v>
+      </c>
+    </row>
+    <row r="296" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>392</v>
       </c>
@@ -16852,10 +17148,10 @@
         <v>33</v>
       </c>
       <c r="AB296">
-        <v>64.50908</v>
+        <v>64.509079999999997</v>
       </c>
       <c r="AC296">
-        <v>-94.65714</v>
+        <v>-94.657139999999998</v>
       </c>
       <c r="AD296">
         <v>15700139</v>
@@ -16864,7 +17160,7 @@
         <v>15700139.08</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>570</v>
       </c>
@@ -16899,7 +17195,7 @@
         <v>33</v>
       </c>
       <c r="AB297">
-        <v>-20.22134</v>
+        <v>-20.221340000000001</v>
       </c>
       <c r="AC297">
         <v>-174.76593</v>
@@ -16908,10 +17204,10 @@
         <v>666812</v>
       </c>
       <c r="AE297">
-        <v>666812.0242</v>
-      </c>
-    </row>
-    <row r="298">
+        <v>666812.02419999999</v>
+      </c>
+    </row>
+    <row r="298" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>572</v>
       </c>
@@ -16946,10 +17242,10 @@
         <v>33</v>
       </c>
       <c r="AB298">
-        <v>17.93255</v>
+        <v>17.932549999999999</v>
       </c>
       <c r="AC298">
-        <v>-62.62858</v>
+        <v>-62.628579999999999</v>
       </c>
       <c r="AD298">
         <v>4203</v>
@@ -16958,7 +17254,7 @@
         <v>4203.437535</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>574</v>
       </c>
@@ -16993,19 +17289,19 @@
         <v>33</v>
       </c>
       <c r="AB299">
-        <v>6.68793</v>
+        <v>6.6879299999999997</v>
       </c>
       <c r="AC299">
-        <v>-162.89879</v>
+        <v>-162.89878999999999</v>
       </c>
       <c r="AD299">
         <v>353676</v>
       </c>
       <c r="AE299">
-        <v>353675.8936</v>
-      </c>
-    </row>
-    <row r="300">
+        <v>353675.89360000001</v>
+      </c>
+    </row>
+    <row r="300" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>575</v>
       </c>
@@ -17067,7 +17363,7 @@
         <v>15.47035</v>
       </c>
       <c r="AC300">
-        <v>-79.14572</v>
+        <v>-79.145719999999997</v>
       </c>
       <c r="AD300">
         <v>15247</v>
@@ -17076,7 +17372,7 @@
         <v>15247.29485</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>576</v>
       </c>
@@ -17111,10 +17407,10 @@
         <v>33</v>
       </c>
       <c r="AB301">
-        <v>42.5007</v>
+        <v>42.500700000000002</v>
       </c>
       <c r="AC301">
-        <v>19.07364</v>
+        <v>19.073640000000001</v>
       </c>
       <c r="AD301">
         <v>20237</v>
@@ -17123,7 +17419,7 @@
         <v>20237.20393</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>52</v>
       </c>
@@ -17161,7 +17457,7 @@
         <v>62.59187</v>
       </c>
       <c r="AC302">
-        <v>-6.99635</v>
+        <v>-6.9963499999999996</v>
       </c>
       <c r="AD302">
         <v>266742</v>
@@ -17170,7 +17466,7 @@
         <v>266742.342</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>578</v>
       </c>
@@ -17205,19 +17501,19 @@
         <v>33</v>
       </c>
       <c r="AB303">
-        <v>44.16895</v>
+        <v>44.168950000000002</v>
       </c>
       <c r="AC303">
-        <v>17.79085</v>
+        <v>17.790849999999999</v>
       </c>
       <c r="AD303">
         <v>50998</v>
       </c>
       <c r="AE303">
-        <v>50997.81703</v>
-      </c>
-    </row>
-    <row r="304">
+        <v>50997.817029999998</v>
+      </c>
+    </row>
+    <row r="304" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>401</v>
       </c>
@@ -17252,19 +17548,19 @@
         <v>33</v>
       </c>
       <c r="AB304">
-        <v>25.7069</v>
+        <v>25.706900000000001</v>
       </c>
       <c r="AC304">
-        <v>51.69541</v>
+        <v>51.695410000000003</v>
       </c>
       <c r="AD304">
         <v>42976</v>
       </c>
       <c r="AE304">
-        <v>42976.44118</v>
-      </c>
-    </row>
-    <row r="305">
+        <v>42976.441180000002</v>
+      </c>
+    </row>
+    <row r="305" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>580</v>
       </c>
@@ -17296,7 +17592,7 @@
         <v>59</v>
       </c>
       <c r="AB305">
-        <v>8.63195</v>
+        <v>8.6319499999999998</v>
       </c>
       <c r="AC305">
         <v>39.63514</v>
@@ -17305,10 +17601,10 @@
         <v>1129077</v>
       </c>
       <c r="AE305">
-        <v>1129076.695</v>
-      </c>
-    </row>
-    <row r="306">
+        <v>1129076.6950000001</v>
+      </c>
+    </row>
+    <row r="306" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>582</v>
       </c>
@@ -17367,10 +17663,10 @@
         <v>39</v>
       </c>
       <c r="AB306">
-        <v>20.89448</v>
+        <v>20.894480000000001</v>
       </c>
       <c r="AC306">
-        <v>-66.84125</v>
+        <v>-66.841250000000002</v>
       </c>
       <c r="AD306">
         <v>18297</v>
@@ -17379,7 +17675,7 @@
         <v>18296.8053</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>583</v>
       </c>
@@ -17417,7 +17713,7 @@
         <v>22.35267</v>
       </c>
       <c r="AC307">
-        <v>90.40713</v>
+        <v>90.407129999999995</v>
       </c>
       <c r="AD307">
         <v>250237</v>
@@ -17426,7 +17722,7 @@
         <v>250237.1507</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>585</v>
       </c>
@@ -17461,19 +17757,19 @@
         <v>33</v>
       </c>
       <c r="AB308">
-        <v>-12.03147</v>
+        <v>-12.031470000000001</v>
       </c>
       <c r="AC308">
-        <v>96.85433999999999</v>
+        <v>96.854339999999993</v>
       </c>
       <c r="AD308">
         <v>467457</v>
       </c>
       <c r="AE308">
-        <v>467456.8656</v>
-      </c>
-    </row>
-    <row r="309">
+        <v>467456.86560000002</v>
+      </c>
+    </row>
+    <row r="309" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>587</v>
       </c>
@@ -17505,19 +17801,19 @@
         <v>59</v>
       </c>
       <c r="AB309">
-        <v>-22.18758</v>
+        <v>-22.187580000000001</v>
       </c>
       <c r="AC309">
-        <v>23.81488</v>
+        <v>23.814879999999999</v>
       </c>
       <c r="AD309">
         <v>578166</v>
       </c>
       <c r="AE309">
-        <v>578166.1666999999</v>
-      </c>
-    </row>
-    <row r="310">
+        <v>578166.16669999994</v>
+      </c>
+    </row>
+    <row r="310" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>589</v>
       </c>
@@ -17549,19 +17845,19 @@
         <v>59</v>
       </c>
       <c r="AB310">
-        <v>33.83078</v>
+        <v>33.830779999999997</v>
       </c>
       <c r="AC310">
-        <v>66.02572000000001</v>
+        <v>66.025720000000007</v>
       </c>
       <c r="AD310">
         <v>641860</v>
       </c>
       <c r="AE310">
-        <v>641860.3931</v>
-      </c>
-    </row>
-    <row r="311">
+        <v>641860.39309999999</v>
+      </c>
+    </row>
+    <row r="311" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>591</v>
       </c>
@@ -17596,7 +17892,7 @@
         <v>33</v>
       </c>
       <c r="AB311">
-        <v>40.29005</v>
+        <v>40.290050000000001</v>
       </c>
       <c r="AC311">
         <v>48.88111</v>
@@ -17605,10 +17901,10 @@
         <v>166590</v>
       </c>
       <c r="AE311">
-        <v>166590.1638</v>
-      </c>
-    </row>
-    <row r="312">
+        <v>166590.16380000001</v>
+      </c>
+    </row>
+    <row r="312" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>593</v>
       </c>
@@ -17643,19 +17939,19 @@
         <v>33</v>
       </c>
       <c r="AB312">
-        <v>5.87993</v>
+        <v>5.8799299999999999</v>
       </c>
       <c r="AC312">
-        <v>113.54819</v>
+        <v>113.54819000000001</v>
       </c>
       <c r="AD312">
         <v>48854</v>
       </c>
       <c r="AE312">
-        <v>48853.87613</v>
-      </c>
-    </row>
-    <row r="313">
+        <v>48853.876129999997</v>
+      </c>
+    </row>
+    <row r="313" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>595</v>
       </c>
@@ -17693,16 +17989,16 @@
         <v>29.2866</v>
       </c>
       <c r="AC313">
-        <v>47.99796</v>
+        <v>47.997959999999999</v>
       </c>
       <c r="AD313">
         <v>28241</v>
       </c>
       <c r="AE313">
-        <v>28241.48885</v>
-      </c>
-    </row>
-    <row r="314">
+        <v>28241.488850000002</v>
+      </c>
+    </row>
+    <row r="314" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>188</v>
       </c>
@@ -17737,19 +18033,19 @@
         <v>33</v>
       </c>
       <c r="AB314">
-        <v>32.24737</v>
+        <v>32.247369999999997</v>
       </c>
       <c r="AC314">
-        <v>-7.75325</v>
+        <v>-7.7532500000000004</v>
       </c>
       <c r="AD314">
         <v>686692</v>
       </c>
       <c r="AE314">
-        <v>686691.5903</v>
-      </c>
-    </row>
-    <row r="315">
+        <v>686691.59030000004</v>
+      </c>
+    </row>
+    <row r="315" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>80</v>
       </c>
@@ -17784,19 +18080,19 @@
         <v>33</v>
       </c>
       <c r="AB315">
-        <v>0.77649</v>
+        <v>0.77649000000000001</v>
       </c>
       <c r="AC315">
-        <v>6.35611</v>
+        <v>6.3561100000000001</v>
       </c>
       <c r="AD315">
         <v>131846</v>
       </c>
       <c r="AE315">
-        <v>131846.4427</v>
-      </c>
-    </row>
-    <row r="316">
+        <v>131846.44270000001</v>
+      </c>
+    </row>
+    <row r="316" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>597</v>
       </c>
@@ -17831,19 +18127,19 @@
         <v>33</v>
       </c>
       <c r="AB316">
-        <v>4.53429</v>
+        <v>4.5342900000000004</v>
       </c>
       <c r="AC316">
-        <v>-9.93744</v>
+        <v>-9.9374400000000005</v>
       </c>
       <c r="AD316">
         <v>347612</v>
       </c>
       <c r="AE316">
-        <v>347612.3157</v>
-      </c>
-    </row>
-    <row r="317">
+        <v>347612.31569999998</v>
+      </c>
+    </row>
+    <row r="317" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>599</v>
       </c>
@@ -17899,19 +18195,19 @@
         <v>33</v>
       </c>
       <c r="AB317">
-        <v>19.50326</v>
+        <v>19.503260000000001</v>
       </c>
       <c r="AC317">
-        <v>166.53046</v>
+        <v>166.53046000000001</v>
       </c>
       <c r="AD317">
         <v>406978</v>
       </c>
       <c r="AE317">
-        <v>406978.1513000001</v>
-      </c>
-    </row>
-    <row r="318">
+        <v>406978.15130000009</v>
+      </c>
+    </row>
+    <row r="318" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>323</v>
       </c>
@@ -17946,10 +18242,10 @@
         <v>33</v>
       </c>
       <c r="AB318">
-        <v>5.73575</v>
+        <v>5.7357500000000003</v>
       </c>
       <c r="AC318">
-        <v>-75.02012000000001</v>
+        <v>-75.020120000000006</v>
       </c>
       <c r="AD318">
         <v>1855095</v>
@@ -17958,7 +18254,7 @@
         <v>1855095.355</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>601</v>
       </c>
@@ -17996,16 +18292,16 @@
         <v>20.38607</v>
       </c>
       <c r="AC319">
-        <v>-64.505</v>
+        <v>-64.504999999999995</v>
       </c>
       <c r="AD319">
         <v>81722</v>
       </c>
       <c r="AE319">
-        <v>81722.13214</v>
-      </c>
-    </row>
-    <row r="320">
+        <v>81722.132140000002</v>
+      </c>
+    </row>
+    <row r="320" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>603</v>
       </c>
@@ -18040,7 +18336,7 @@
         <v>33</v>
       </c>
       <c r="AB320">
-        <v>78.72631</v>
+        <v>78.726309999999998</v>
       </c>
       <c r="AC320">
         <v>18.32104</v>
@@ -18049,10 +18345,10 @@
         <v>857625</v>
       </c>
       <c r="AE320">
-        <v>857624.7462000002</v>
-      </c>
-    </row>
-    <row r="321">
+        <v>857624.74620000017</v>
+      </c>
+    </row>
+    <row r="321" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>66</v>
       </c>
@@ -18090,16 +18386,16 @@
         <v>-11.42789</v>
       </c>
       <c r="AC321">
-        <v>43.45654</v>
+        <v>43.456539999999997</v>
       </c>
       <c r="AD321">
         <v>166149</v>
       </c>
       <c r="AE321">
-        <v>166148.6598</v>
-      </c>
-    </row>
-    <row r="322">
+        <v>166148.65979999999</v>
+      </c>
+    </row>
+    <row r="322" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>604</v>
       </c>
@@ -18134,7 +18430,7 @@
         <v>33</v>
       </c>
       <c r="AB322">
-        <v>-0.59113</v>
+        <v>-0.59113000000000004</v>
       </c>
       <c r="AC322">
         <v>166.12402</v>
@@ -18143,10 +18439,10 @@
         <v>309283</v>
       </c>
       <c r="AE322">
-        <v>309282.8981</v>
-      </c>
-    </row>
-    <row r="323">
+        <v>309282.89809999999</v>
+      </c>
+    </row>
+    <row r="323" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>606</v>
       </c>
@@ -18181,7 +18477,7 @@
         <v>33</v>
       </c>
       <c r="AB323">
-        <v>58.7153</v>
+        <v>58.715299999999999</v>
       </c>
       <c r="AC323">
         <v>24.40898</v>
@@ -18190,10 +18486,10 @@
         <v>81842</v>
       </c>
       <c r="AE323">
-        <v>81842.11413</v>
-      </c>
-    </row>
-    <row r="324">
+        <v>81842.114130000002</v>
+      </c>
+    </row>
+    <row r="324" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>242</v>
       </c>
@@ -18231,7 +18527,7 @@
         <v>10.92648</v>
       </c>
       <c r="AC324">
-        <v>-16.94227</v>
+        <v>-16.942270000000001</v>
       </c>
       <c r="AD324">
         <v>140612</v>
@@ -18240,7 +18536,7 @@
         <v>140611.56</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>608</v>
       </c>
@@ -18275,19 +18571,19 @@
         <v>33</v>
       </c>
       <c r="AB325">
-        <v>39.20596</v>
+        <v>39.205959999999997</v>
       </c>
       <c r="AC325">
-        <v>58.459</v>
+        <v>58.459000000000003</v>
       </c>
       <c r="AD325">
         <v>550026</v>
       </c>
       <c r="AE325">
-        <v>550026.2555</v>
-      </c>
-    </row>
-    <row r="326">
+        <v>550026.25549999997</v>
+      </c>
+    </row>
+    <row r="326" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>610</v>
       </c>
@@ -18319,19 +18615,19 @@
         <v>33</v>
       </c>
       <c r="AB326">
-        <v>-54.42184</v>
+        <v>-54.421840000000003</v>
       </c>
       <c r="AC326">
-        <v>3.35837</v>
+        <v>3.3583699999999999</v>
       </c>
       <c r="AD326">
         <v>51</v>
       </c>
       <c r="AE326">
-        <v>50.71955487</v>
-      </c>
-    </row>
-    <row r="327">
+        <v>50.719554870000003</v>
+      </c>
+    </row>
+    <row r="327" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>612</v>
       </c>
@@ -18375,10 +18671,10 @@
         <v>376110</v>
       </c>
       <c r="AE327">
-        <v>376110.1204</v>
-      </c>
-    </row>
-    <row r="328">
+        <v>376110.12040000001</v>
+      </c>
+    </row>
+    <row r="328" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>614</v>
       </c>
@@ -18413,7 +18709,7 @@
         <v>33</v>
       </c>
       <c r="AB328">
-        <v>-20.86104</v>
+        <v>-20.861039999999999</v>
       </c>
       <c r="AC328">
         <v>39.42539</v>
@@ -18425,7 +18721,7 @@
         <v>120802.1517</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" spans="1:31" ht="12.9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>615</v>
       </c>
@@ -18463,7 +18759,7 @@
         <v>14.11872</v>
       </c>
       <c r="AC329">
-        <v>-91.23143</v>
+        <v>-91.231430000000003</v>
       </c>
       <c r="AD329">
         <v>218932</v>
@@ -18473,5 +18769,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>